--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albuq\Documents\SPTECH\TermoChain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F57B53-8656-44EF-ACC5-BAE9DAD79400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BBD663-2B8F-404B-A035-3EA7C7743808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="116">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -341,20 +366,56 @@
     <t>SP03</t>
   </si>
   <si>
-    <t>DIAS</t>
-  </si>
-  <si>
-    <t>META DIA</t>
-  </si>
-  <si>
-    <t>META IDEAL</t>
+    <t>Pontos a Serem Entregues</t>
+  </si>
+  <si>
+    <t>Prazo de Término (DIAS)</t>
+  </si>
+  <si>
+    <t>Média Ideal por Dias</t>
+  </si>
+  <si>
+    <t>Dias</t>
+  </si>
+  <si>
+    <t>Meta Dia</t>
+  </si>
+  <si>
+    <t>Meta Ideal</t>
+  </si>
+  <si>
+    <t>Realizado Dia Ideal</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>SPRINT</t>
+  </si>
+  <si>
+    <t>SPRINT1</t>
+  </si>
+  <si>
+    <t>SPRINT2</t>
+  </si>
+  <si>
+    <t>SPRINT3</t>
+  </si>
+  <si>
+    <t>INTERVALO ASSUMIDO</t>
+  </si>
+  <si>
+    <t>10/02/26 - 03/06/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,16 +443,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -404,8 +457,86 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -456,11 +587,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -472,12 +612,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,6 +699,2130 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Gráfico</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> de Burnwdown</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Meta Ideal</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$P$3:$P$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="115"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>269</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>263</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>248</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>236</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>233</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>221</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>209</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>206</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>203</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>182</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>161</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>152</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>149</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>146</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>119</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>116</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>107</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>104</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>101</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>92</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E76B-431C-A1EB-63A447025E13}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Pendente</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$R$3:$R$117</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="115"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>267</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>266</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>257</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>242</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>239</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>231</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>194</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>173</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>167</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>129</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>111</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E76B-431C-A1EB-63A447025E13}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:smooth val="0"/>
+        <c:axId val="2033779343"/>
+        <c:axId val="2033781263"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2033779343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1600"/>
+                  <a:t>Dias</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2033781263"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2033781263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="2000"/>
+                  <a:t>Pontos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2033779343"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>599515</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>169208</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>997323</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7A8D6-70E4-917E-B829-328A6B8B2288}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Planilha1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="N1" t="str">
+            <v>Meta Ideal</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>Pendente</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>360</v>
+          </cell>
+          <cell r="O2">
+            <v>370</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="M3">
+            <v>1</v>
+          </cell>
+          <cell r="N3">
+            <v>348</v>
+          </cell>
+          <cell r="O3">
+            <v>358</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="M4">
+            <v>2</v>
+          </cell>
+          <cell r="N4">
+            <v>336</v>
+          </cell>
+          <cell r="O4">
+            <v>346</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="M5">
+            <v>3</v>
+          </cell>
+          <cell r="N5">
+            <v>324</v>
+          </cell>
+          <cell r="O5">
+            <v>334</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="M6">
+            <v>4</v>
+          </cell>
+          <cell r="N6">
+            <v>312</v>
+          </cell>
+          <cell r="O6">
+            <v>322</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="M7">
+            <v>5</v>
+          </cell>
+          <cell r="N7">
+            <v>300</v>
+          </cell>
+          <cell r="O7">
+            <v>310</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="M8">
+            <v>6</v>
+          </cell>
+          <cell r="N8">
+            <v>288</v>
+          </cell>
+          <cell r="O8">
+            <v>298</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="M9">
+            <v>7</v>
+          </cell>
+          <cell r="N9">
+            <v>276</v>
+          </cell>
+          <cell r="O9">
+            <v>286</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="M10">
+            <v>8</v>
+          </cell>
+          <cell r="N10">
+            <v>264</v>
+          </cell>
+          <cell r="O10">
+            <v>274</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="M11">
+            <v>9</v>
+          </cell>
+          <cell r="N11">
+            <v>252</v>
+          </cell>
+          <cell r="O11">
+            <v>262</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="M12">
+            <v>10</v>
+          </cell>
+          <cell r="N12">
+            <v>240</v>
+          </cell>
+          <cell r="O12">
+            <v>240</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="M13">
+            <v>11</v>
+          </cell>
+          <cell r="N13">
+            <v>228</v>
+          </cell>
+          <cell r="O13">
+            <v>228</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="M14">
+            <v>12</v>
+          </cell>
+          <cell r="N14">
+            <v>216</v>
+          </cell>
+          <cell r="O14">
+            <v>216</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="M15">
+            <v>13</v>
+          </cell>
+          <cell r="N15">
+            <v>204</v>
+          </cell>
+          <cell r="O15">
+            <v>204</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="M16">
+            <v>14</v>
+          </cell>
+          <cell r="N16">
+            <v>192</v>
+          </cell>
+          <cell r="O16">
+            <v>192</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="M17">
+            <v>15</v>
+          </cell>
+          <cell r="N17">
+            <v>180</v>
+          </cell>
+          <cell r="O17">
+            <v>180</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="M18">
+            <v>16</v>
+          </cell>
+          <cell r="N18">
+            <v>168</v>
+          </cell>
+          <cell r="O18">
+            <v>168</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="M19">
+            <v>17</v>
+          </cell>
+          <cell r="N19">
+            <v>156</v>
+          </cell>
+          <cell r="O19">
+            <v>156</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="M20">
+            <v>18</v>
+          </cell>
+          <cell r="N20">
+            <v>144</v>
+          </cell>
+          <cell r="O20">
+            <v>144</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="M21">
+            <v>19</v>
+          </cell>
+          <cell r="N21">
+            <v>132</v>
+          </cell>
+          <cell r="O21">
+            <v>132</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="M22">
+            <v>20</v>
+          </cell>
+          <cell r="N22">
+            <v>120</v>
+          </cell>
+          <cell r="O22">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="M23">
+            <v>21</v>
+          </cell>
+          <cell r="N23">
+            <v>108</v>
+          </cell>
+          <cell r="O23">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="M24">
+            <v>22</v>
+          </cell>
+          <cell r="N24">
+            <v>96</v>
+          </cell>
+          <cell r="O24">
+            <v>86</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="M25">
+            <v>23</v>
+          </cell>
+          <cell r="N25">
+            <v>84</v>
+          </cell>
+          <cell r="O25">
+            <v>74</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="M26">
+            <v>24</v>
+          </cell>
+          <cell r="N26">
+            <v>72</v>
+          </cell>
+          <cell r="O26">
+            <v>62</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="M27">
+            <v>25</v>
+          </cell>
+          <cell r="N27">
+            <v>60</v>
+          </cell>
+          <cell r="O27">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="M28">
+            <v>26</v>
+          </cell>
+          <cell r="N28">
+            <v>48</v>
+          </cell>
+          <cell r="O28">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="M29">
+            <v>27</v>
+          </cell>
+          <cell r="N29">
+            <v>36</v>
+          </cell>
+          <cell r="O29">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="M30">
+            <v>28</v>
+          </cell>
+          <cell r="N30">
+            <v>24</v>
+          </cell>
+          <cell r="O30">
+            <v>14</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="M31">
+            <v>29</v>
+          </cell>
+          <cell r="N31">
+            <v>12</v>
+          </cell>
+          <cell r="O31">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="M32">
+            <v>30</v>
+          </cell>
+          <cell r="N32">
+            <v>0</v>
+          </cell>
+          <cell r="O32">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -812,21 +3142,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
-  <dimension ref="A2:R39"/>
+  <dimension ref="A2:T118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="5" max="5" width="45.7109375" customWidth="1"/>
     <col min="6" max="6" width="53.28515625" customWidth="1"/>
     <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
     <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="17" max="17" width="21" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>59</v>
       </c>
       <c r="B2" s="4">
@@ -856,1211 +3196,3629 @@
       <c r="L2" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="N2" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
       <c r="B3" s="4">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="4">
-        <v>3</v>
-      </c>
-      <c r="J3" s="4">
-        <v>3</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="I3" s="23">
+        <v>3</v>
+      </c>
+      <c r="J3" s="21">
+        <v>3</v>
+      </c>
+      <c r="K3" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="N3" s="6">
+        <v>0</v>
+      </c>
+      <c r="O3" s="29">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
+        <f>B8</f>
+        <v>272</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <f>B8</f>
+        <v>272</v>
+      </c>
+      <c r="S3" s="14">
+        <v>46063</v>
+      </c>
+      <c r="T3" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="4">
         <v>8</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="25">
         <v>8</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="20">
         <v>1</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="N4" s="6" cm="1">
+        <f t="array" ref="N4:N117">_xlfn.SEQUENCE(114)</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="29">
+        <f t="shared" ref="O4:O35" si="0">$B$10</f>
+        <v>3</v>
+      </c>
+      <c r="P4" s="6">
+        <f>P3-$O$4</f>
+        <v>269</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <f>R3-Q4</f>
+        <v>272</v>
+      </c>
+      <c r="S4" s="14">
+        <f>S3+1</f>
+        <v>46064</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="4">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="27">
         <v>13</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="20">
         <v>1</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="N5" s="6">
+        <v>2</v>
+      </c>
+      <c r="O5" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P5" s="6">
+        <f t="shared" ref="P5:P68" si="1">P4-$O$4</f>
+        <v>266</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <f>IF(Q5&lt;&gt;"",R4-Q5,R4)</f>
+        <v>272</v>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" ref="S5:S68" si="2">S4+1</f>
+        <v>46065</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="4">
         <v>21</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="27">
         <v>13</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="20">
         <v>1</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="5">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5">
-        <v>12</v>
-      </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E7" s="3" t="s">
+      <c r="N6" s="6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" si="1"/>
+        <v>263</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>2</v>
+      </c>
+      <c r="R6" s="6">
+        <f t="shared" ref="R6:R69" si="3">IF(Q6&lt;&gt;"",R5-Q6,R5)</f>
+        <v>270</v>
+      </c>
+      <c r="S6" s="14">
+        <f t="shared" si="2"/>
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="27">
         <v>13</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="22">
         <v>2</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="6">
+        <v>4</v>
+      </c>
+      <c r="O7" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="S7" s="14">
+        <f t="shared" si="2"/>
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="6">
+        <f>SUM(I3:I39)</f>
+        <v>272</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="25">
+        <v>8</v>
+      </c>
+      <c r="J8" s="20">
         <v>1</v>
       </c>
-      <c r="O7" s="5">
-        <v>12</v>
-      </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="4">
-        <v>8</v>
-      </c>
-      <c r="J8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="6">
+        <v>5</v>
+      </c>
+      <c r="O8" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="1"/>
+        <v>257</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>3</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="3"/>
+        <v>267</v>
+      </c>
+      <c r="S8" s="14">
+        <f t="shared" si="2"/>
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="6">
+        <v>114</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="24">
+        <v>5</v>
+      </c>
+      <c r="J9" s="22">
         <v>2</v>
       </c>
-      <c r="O8" s="5">
-        <v>12</v>
-      </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="4">
-        <v>5</v>
-      </c>
-      <c r="J9" s="4">
-        <v>2</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N9" s="5">
-        <v>3</v>
-      </c>
-      <c r="O9" s="5">
-        <v>12</v>
-      </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E10" s="3" t="s">
+      <c r="N9" s="6">
+        <v>6</v>
+      </c>
+      <c r="O9" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="1"/>
+        <v>254</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" si="3"/>
+        <v>266</v>
+      </c>
+      <c r="S9" s="14">
+        <f t="shared" si="2"/>
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="6">
+        <f>ROUNDUP(B8/B9, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="4">
-        <v>3</v>
-      </c>
-      <c r="J10" s="4">
-        <v>3</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="I10" s="23">
+        <v>3</v>
+      </c>
+      <c r="J10" s="21">
+        <v>3</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="6">
+        <v>7</v>
+      </c>
+      <c r="O10" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" si="1"/>
+        <v>251</v>
+      </c>
+      <c r="Q10" s="6">
         <v>4</v>
       </c>
-      <c r="O10" s="5">
-        <v>12</v>
-      </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E11" s="3" t="s">
+      <c r="R10" s="6">
+        <f t="shared" si="3"/>
+        <v>262</v>
+      </c>
+      <c r="S10" s="14">
+        <f t="shared" si="2"/>
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="27">
         <v>13</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="20">
         <v>1</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N11" s="5">
-        <v>5</v>
-      </c>
-      <c r="O11" s="5">
-        <v>12</v>
-      </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E12" s="3" t="s">
+      <c r="N11" s="6">
+        <v>8</v>
+      </c>
+      <c r="O11" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="1"/>
+        <v>248</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <f t="shared" si="3"/>
+        <v>262</v>
+      </c>
+      <c r="S11" s="14">
+        <f t="shared" si="2"/>
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="25">
         <v>8</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="20">
         <v>1</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="5">
-        <v>6</v>
-      </c>
-      <c r="O12" s="5">
-        <v>12</v>
-      </c>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E13" s="3" t="s">
+      <c r="N12" s="6">
+        <v>9</v>
+      </c>
+      <c r="O12" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="1"/>
+        <v>245</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>5</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+      <c r="S12" s="14">
+        <f t="shared" si="2"/>
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="E13" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="24">
         <v>5</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="22">
         <v>2</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="5">
-        <v>7</v>
-      </c>
-      <c r="O13" s="5">
-        <v>12</v>
-      </c>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E14" s="3" t="s">
+      <c r="N13" s="6">
+        <v>10</v>
+      </c>
+      <c r="O13" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="1"/>
+        <v>242</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2</v>
+      </c>
+      <c r="R13" s="6">
+        <f t="shared" si="3"/>
+        <v>255</v>
+      </c>
+      <c r="S13" s="14">
+        <f t="shared" si="2"/>
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="E14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="24">
         <v>5</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="22">
         <v>2</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="5">
-        <v>8</v>
-      </c>
-      <c r="O14" s="5">
+      <c r="N14" s="6">
+        <v>11</v>
+      </c>
+      <c r="O14" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="1"/>
+        <v>239</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>6</v>
+      </c>
+      <c r="R14" s="6">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="S14" s="14">
+        <f t="shared" si="2"/>
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="4">
-        <v>3</v>
-      </c>
-      <c r="J15" s="4">
-        <v>3</v>
-      </c>
-      <c r="K15" s="4" t="s">
+      <c r="I15" s="23">
+        <v>3</v>
+      </c>
+      <c r="J15" s="21">
+        <v>3</v>
+      </c>
+      <c r="K15" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="N15" s="5">
-        <v>9</v>
-      </c>
-      <c r="O15" s="5">
+      <c r="N15" s="6">
         <v>12</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="E16" s="3" t="s">
+      <c r="O15" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="1"/>
+        <v>236</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="S15" s="14">
+        <f t="shared" si="2"/>
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="24">
         <v>5</v>
       </c>
-      <c r="J16" s="4">
-        <v>3</v>
-      </c>
-      <c r="K16" s="4" t="s">
+      <c r="J16" s="21">
+        <v>3</v>
+      </c>
+      <c r="K16" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="N16" s="5">
-        <v>10</v>
-      </c>
-      <c r="O16" s="5">
-        <v>12</v>
-      </c>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E17" s="3" t="s">
+      <c r="N16" s="6">
+        <v>13</v>
+      </c>
+      <c r="O16" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="1"/>
+        <v>233</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>7</v>
+      </c>
+      <c r="R16" s="6">
+        <f t="shared" si="3"/>
+        <v>242</v>
+      </c>
+      <c r="S16" s="14">
+        <f t="shared" si="2"/>
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I17" s="4">
-        <v>3</v>
-      </c>
-      <c r="J17" s="4">
+      <c r="I17" s="23">
+        <v>3</v>
+      </c>
+      <c r="J17" s="20">
         <v>1</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N17" s="5">
-        <v>11</v>
-      </c>
-      <c r="O17" s="5">
-        <v>12</v>
-      </c>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E18" s="3" t="s">
+      <c r="N17" s="6">
+        <v>14</v>
+      </c>
+      <c r="O17" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="1"/>
+        <v>230</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>3</v>
+      </c>
+      <c r="R17" s="6">
+        <f t="shared" si="3"/>
+        <v>239</v>
+      </c>
+      <c r="S17" s="14">
+        <f t="shared" si="2"/>
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E18" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="24">
         <v>5</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="20">
         <v>1</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="24" t="s">
         <v>56</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N18" s="5">
-        <v>12</v>
-      </c>
-      <c r="O18" s="5">
-        <v>12</v>
-      </c>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-    </row>
-    <row r="19" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E19" s="3" t="s">
+      <c r="N18" s="6">
+        <v>15</v>
+      </c>
+      <c r="O18" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="1"/>
+        <v>227</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>8</v>
+      </c>
+      <c r="R18" s="6">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="S18" s="14">
+        <f t="shared" si="2"/>
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4">
+      <c r="H19" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="23">
+        <v>3</v>
+      </c>
+      <c r="J19" s="22">
         <v>2</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="N19" s="5">
-        <v>13</v>
-      </c>
-      <c r="O19" s="5">
-        <v>12</v>
-      </c>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E20" s="3" t="s">
+      <c r="N19" s="6">
+        <v>16</v>
+      </c>
+      <c r="O19" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P19" s="6">
+        <f t="shared" si="1"/>
+        <v>224</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="S19" s="14">
+        <f t="shared" si="2"/>
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4">
+      <c r="H20" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="23">
+        <v>3</v>
+      </c>
+      <c r="J20" s="22">
         <v>2</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L20" s="4"/>
-      <c r="N20" s="5">
-        <v>14</v>
-      </c>
-      <c r="O20" s="5">
-        <v>12</v>
-      </c>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-    </row>
-    <row r="21" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E21" s="3" t="s">
+      <c r="N20" s="6">
+        <v>17</v>
+      </c>
+      <c r="O20" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="1"/>
+        <v>221</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>9</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="3"/>
+        <v>222</v>
+      </c>
+      <c r="S20" s="14">
+        <f t="shared" si="2"/>
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E21" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4">
-        <v>3</v>
-      </c>
-      <c r="K21" s="4" t="s">
+      <c r="H21" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="25">
+        <v>8</v>
+      </c>
+      <c r="J21" s="21">
+        <v>3</v>
+      </c>
+      <c r="K21" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="N21" s="5">
-        <v>15</v>
-      </c>
-      <c r="O21" s="5">
-        <v>12</v>
-      </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-    </row>
-    <row r="22" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E22" s="3" t="s">
+      <c r="N21" s="6">
+        <v>18</v>
+      </c>
+      <c r="O21" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="1"/>
+        <v>218</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>4</v>
+      </c>
+      <c r="R21" s="6">
+        <f t="shared" si="3"/>
+        <v>218</v>
+      </c>
+      <c r="S21" s="14">
+        <f t="shared" si="2"/>
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E22" s="19" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4">
+      <c r="H22" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="27">
+        <v>13</v>
+      </c>
+      <c r="J22" s="20">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="N22" s="5">
-        <v>16</v>
-      </c>
-      <c r="O22" s="5">
-        <v>12</v>
-      </c>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-    </row>
-    <row r="23" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E23" s="3" t="s">
+      <c r="N22" s="6">
+        <v>19</v>
+      </c>
+      <c r="O22" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" si="1"/>
+        <v>215</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>10</v>
+      </c>
+      <c r="R22" s="6">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+      <c r="S22" s="14">
+        <f t="shared" si="2"/>
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E23" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4">
+      <c r="H23" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="27">
+        <v>13</v>
+      </c>
+      <c r="J23" s="20">
         <v>1</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="N23" s="5">
-        <v>17</v>
-      </c>
-      <c r="O23" s="5">
-        <v>12</v>
-      </c>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-    </row>
-    <row r="24" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E24" s="3" t="s">
+      <c r="N23" s="6">
+        <v>20</v>
+      </c>
+      <c r="O23" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="1"/>
+        <v>212</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="3"/>
+        <v>208</v>
+      </c>
+      <c r="S23" s="14">
+        <f t="shared" si="2"/>
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E24" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4">
+      <c r="H24" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="25">
+        <v>8</v>
+      </c>
+      <c r="J24" s="22">
         <v>2</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N24" s="5">
-        <v>18</v>
-      </c>
-      <c r="O24" s="5">
-        <v>12</v>
-      </c>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-    </row>
-    <row r="25" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E25" s="3" t="s">
+      <c r="N24" s="6">
+        <v>21</v>
+      </c>
+      <c r="O24" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P24" s="6">
+        <f t="shared" si="1"/>
+        <v>209</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>8</v>
+      </c>
+      <c r="R24" s="6">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="S24" s="14">
+        <f t="shared" si="2"/>
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E25" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4">
+      <c r="H25" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="25">
+        <v>8</v>
+      </c>
+      <c r="J25" s="22">
         <v>2</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L25" s="4"/>
-      <c r="N25" s="5">
-        <v>19</v>
-      </c>
-      <c r="O25" s="5">
-        <v>12</v>
-      </c>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-    </row>
-    <row r="26" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E26" s="3" t="s">
+      <c r="N25" s="6">
+        <v>22</v>
+      </c>
+      <c r="O25" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P25" s="6">
+        <f t="shared" si="1"/>
+        <v>206</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>6</v>
+      </c>
+      <c r="R25" s="6">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+      <c r="S25" s="14">
+        <f t="shared" si="2"/>
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E26" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4">
-        <v>3</v>
-      </c>
-      <c r="K26" s="4" t="s">
+      <c r="H26" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="23">
+        <v>3</v>
+      </c>
+      <c r="J26" s="21">
+        <v>3</v>
+      </c>
+      <c r="K26" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N26" s="5">
-        <v>20</v>
-      </c>
-      <c r="O26" s="5">
-        <v>12</v>
-      </c>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-    </row>
-    <row r="27" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E27" s="3" t="s">
+      <c r="N26" s="6">
+        <v>23</v>
+      </c>
+      <c r="O26" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="1"/>
+        <v>203</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>9</v>
+      </c>
+      <c r="R26" s="6">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="S26" s="14">
+        <f t="shared" si="2"/>
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4">
-        <v>3</v>
-      </c>
-      <c r="K27" s="4" t="s">
+      <c r="H27" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="24">
+        <v>5</v>
+      </c>
+      <c r="J27" s="21">
+        <v>3</v>
+      </c>
+      <c r="K27" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N27" s="5">
-        <v>21</v>
-      </c>
-      <c r="O27" s="5">
-        <v>12</v>
-      </c>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-    </row>
-    <row r="28" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E28" s="3" t="s">
+      <c r="N27" s="6">
+        <v>24</v>
+      </c>
+      <c r="O27" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P27" s="6">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="S27" s="14">
+        <f t="shared" si="2"/>
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="28" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E28" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4">
+      <c r="H28" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" s="25">
+        <v>8</v>
+      </c>
+      <c r="J28" s="20">
         <v>1</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N28" s="5">
-        <v>22</v>
-      </c>
-      <c r="O28" s="5">
-        <v>12</v>
-      </c>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-    </row>
-    <row r="29" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E29" s="3" t="s">
+      <c r="N28" s="6">
+        <v>25</v>
+      </c>
+      <c r="O28" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P28" s="6">
+        <f t="shared" si="1"/>
+        <v>197</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>7</v>
+      </c>
+      <c r="R28" s="6">
+        <f t="shared" si="3"/>
+        <v>178</v>
+      </c>
+      <c r="S28" s="14">
+        <f t="shared" si="2"/>
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E29" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4">
+      <c r="H29" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="25">
+        <v>8</v>
+      </c>
+      <c r="J29" s="22">
         <v>2</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N29" s="5">
-        <v>23</v>
-      </c>
-      <c r="O29" s="5">
-        <v>12</v>
-      </c>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-    </row>
-    <row r="30" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E30" s="3" t="s">
+      <c r="N29" s="6">
+        <v>26</v>
+      </c>
+      <c r="O29" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P29" s="6">
+        <f t="shared" si="1"/>
+        <v>194</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>5</v>
+      </c>
+      <c r="R29" s="6">
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+      <c r="S29" s="14">
+        <f t="shared" si="2"/>
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E30" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4">
+      <c r="H30" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I30" s="24">
+        <v>5</v>
+      </c>
+      <c r="J30" s="20">
         <v>1</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="N30" s="5">
-        <v>24</v>
-      </c>
-      <c r="O30" s="5">
-        <v>12</v>
-      </c>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-    </row>
-    <row r="31" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E31" s="3" t="s">
+      <c r="N30" s="6">
+        <v>27</v>
+      </c>
+      <c r="O30" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P30" s="6">
+        <f t="shared" si="1"/>
+        <v>191</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>6</v>
+      </c>
+      <c r="R30" s="6">
+        <f t="shared" si="3"/>
+        <v>167</v>
+      </c>
+      <c r="S30" s="14">
+        <f t="shared" si="2"/>
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E31" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4">
+      <c r="H31" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="24">
+        <v>5</v>
+      </c>
+      <c r="J31" s="20">
         <v>1</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L31" s="4"/>
-      <c r="N31" s="5">
-        <v>25</v>
-      </c>
-      <c r="O31" s="5">
-        <v>12</v>
-      </c>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-    </row>
-    <row r="32" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E32" s="3" t="s">
+      <c r="N31" s="6">
+        <v>28</v>
+      </c>
+      <c r="O31" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P31" s="6">
+        <f t="shared" si="1"/>
+        <v>188</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <f t="shared" si="3"/>
+        <v>167</v>
+      </c>
+      <c r="S31" s="14">
+        <f t="shared" si="2"/>
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="32" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E32" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4">
-        <v>3</v>
-      </c>
-      <c r="K32" s="4" t="s">
+      <c r="H32" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="24">
+        <v>5</v>
+      </c>
+      <c r="J32" s="21">
+        <v>3</v>
+      </c>
+      <c r="K32" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N32" s="5">
-        <v>26</v>
-      </c>
-      <c r="O32" s="5">
-        <v>12</v>
-      </c>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-    </row>
-    <row r="33" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E33" s="3" t="s">
+      <c r="N32" s="6">
+        <v>29</v>
+      </c>
+      <c r="O32" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P32" s="6">
+        <f t="shared" si="1"/>
+        <v>185</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>4</v>
+      </c>
+      <c r="R32" s="6">
+        <f t="shared" si="3"/>
+        <v>163</v>
+      </c>
+      <c r="S32" s="14">
+        <f t="shared" si="2"/>
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="33" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E33" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4">
-        <v>3</v>
-      </c>
-      <c r="K33" s="4" t="s">
+      <c r="H33" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="23">
+        <v>3</v>
+      </c>
+      <c r="J33" s="21">
+        <v>3</v>
+      </c>
+      <c r="K33" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="N33" s="5">
-        <v>27</v>
-      </c>
-      <c r="O33" s="5">
-        <v>12</v>
-      </c>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-    </row>
-    <row r="34" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E34" s="3" t="s">
+      <c r="N33" s="6">
+        <v>30</v>
+      </c>
+      <c r="O33" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>3</v>
+      </c>
+      <c r="R33" s="6">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="S33" s="14">
+        <f t="shared" si="2"/>
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="34" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4">
+      <c r="H34" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="23">
+        <v>3</v>
+      </c>
+      <c r="J34" s="20">
         <v>1</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="20" t="s">
         <v>88</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="N34" s="5">
-        <v>28</v>
-      </c>
-      <c r="O34" s="5">
-        <v>12</v>
-      </c>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-    </row>
-    <row r="35" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E35" s="3" t="s">
+      <c r="N34" s="6">
+        <v>31</v>
+      </c>
+      <c r="O34" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P34" s="6">
+        <f t="shared" si="1"/>
+        <v>179</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>1</v>
+      </c>
+      <c r="R34" s="6">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="S34" s="14">
+        <f t="shared" si="2"/>
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="35" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E35" s="19" t="s">
         <v>90</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4">
+      <c r="H35" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="27">
+        <v>13</v>
+      </c>
+      <c r="J35" s="22">
         <v>2</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" s="28" t="s">
         <v>100</v>
       </c>
       <c r="L35" s="4"/>
-      <c r="N35" s="5">
-        <v>29</v>
-      </c>
-      <c r="O35" s="5">
-        <v>12</v>
-      </c>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-    </row>
-    <row r="36" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E36" s="3" t="s">
+      <c r="N35" s="6">
+        <v>32</v>
+      </c>
+      <c r="O35" s="29">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="P35" s="6">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>0</v>
+      </c>
+      <c r="R35" s="6">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="S35" s="14">
+        <f t="shared" si="2"/>
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="36" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E36" s="19" t="s">
         <v>91</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4">
-        <v>1</v>
-      </c>
-      <c r="K36" s="4" t="s">
+      <c r="H36" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="I36" s="26">
+        <v>21</v>
+      </c>
+      <c r="J36" s="21">
+        <v>3</v>
+      </c>
+      <c r="K36" s="28" t="s">
         <v>100</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="N36" s="5">
-        <v>30</v>
-      </c>
-      <c r="O36" s="5">
-        <v>12</v>
-      </c>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-    </row>
-    <row r="37" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E37" s="3" t="s">
+      <c r="N36" s="6">
+        <v>33</v>
+      </c>
+      <c r="O36" s="29">
+        <f t="shared" ref="O36:O67" si="4">$B$10</f>
+        <v>3</v>
+      </c>
+      <c r="P36" s="6">
+        <f t="shared" si="1"/>
+        <v>173</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0</v>
+      </c>
+      <c r="R36" s="6">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="S36" s="14">
+        <f t="shared" si="2"/>
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="37" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E37" s="19" t="s">
         <v>92</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4">
+      <c r="H37" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" s="25">
+        <v>8</v>
+      </c>
+      <c r="J37" s="22">
         <v>2</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="28" t="s">
         <v>100</v>
       </c>
       <c r="L37" s="4"/>
-      <c r="N37" s="5">
-        <v>31</v>
-      </c>
-      <c r="O37" s="5">
-        <v>12</v>
-      </c>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-    </row>
-    <row r="38" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E38" s="3" t="s">
+      <c r="N37" s="6">
+        <v>34</v>
+      </c>
+      <c r="O37" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P37" s="6">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>0</v>
+      </c>
+      <c r="R37" s="6">
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="S37" s="14">
+        <f t="shared" si="2"/>
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="38" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E38" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4">
+      <c r="H38" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" s="25">
+        <v>8</v>
+      </c>
+      <c r="J38" s="20">
         <v>1</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="28" t="s">
         <v>100</v>
       </c>
       <c r="L38" s="4"/>
-      <c r="N38" s="5">
-        <v>32</v>
-      </c>
-      <c r="O38" s="5">
-        <v>12</v>
-      </c>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-    </row>
-    <row r="39" spans="5:18" x14ac:dyDescent="0.25">
-      <c r="E39" s="3" t="s">
+      <c r="N38" s="6">
+        <v>35</v>
+      </c>
+      <c r="O38" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P38" s="6">
+        <f t="shared" si="1"/>
+        <v>167</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>8</v>
+      </c>
+      <c r="R38" s="6">
+        <f t="shared" si="3"/>
+        <v>151</v>
+      </c>
+      <c r="S38" s="15">
+        <f t="shared" si="2"/>
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="39" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E39" s="19" t="s">
         <v>94</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4">
+      <c r="H39" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" s="25">
+        <v>8</v>
+      </c>
+      <c r="J39" s="22">
         <v>2</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" s="28" t="s">
         <v>100</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="N39" s="5">
-        <v>33</v>
-      </c>
-      <c r="O39" s="5">
-        <v>12</v>
-      </c>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
+      <c r="N39" s="6">
+        <v>36</v>
+      </c>
+      <c r="O39" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P39" s="6">
+        <f t="shared" si="1"/>
+        <v>164</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6">
+        <f t="shared" si="3"/>
+        <v>151</v>
+      </c>
+      <c r="S39" s="15">
+        <f t="shared" si="2"/>
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="40" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N40" s="6">
+        <v>37</v>
+      </c>
+      <c r="O40" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P40" s="6">
+        <f t="shared" si="1"/>
+        <v>161</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>6</v>
+      </c>
+      <c r="R40" s="6">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+      <c r="S40" s="15">
+        <f t="shared" si="2"/>
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="41" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N41" s="6">
+        <v>38</v>
+      </c>
+      <c r="O41" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P41" s="6">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+      <c r="S41" s="15">
+        <f t="shared" si="2"/>
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="42" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N42" s="6">
+        <v>39</v>
+      </c>
+      <c r="O42" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P42" s="6">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>8</v>
+      </c>
+      <c r="R42" s="6">
+        <f t="shared" si="3"/>
+        <v>137</v>
+      </c>
+      <c r="S42" s="15">
+        <f t="shared" si="2"/>
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="43" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N43" s="6">
+        <v>40</v>
+      </c>
+      <c r="O43" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P43" s="6">
+        <f t="shared" si="1"/>
+        <v>152</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>8</v>
+      </c>
+      <c r="R43" s="6">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+      <c r="S43" s="15">
+        <f t="shared" si="2"/>
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="44" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N44" s="6">
+        <v>41</v>
+      </c>
+      <c r="O44" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P44" s="6">
+        <f t="shared" si="1"/>
+        <v>149</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>0</v>
+      </c>
+      <c r="R44" s="6">
+        <f t="shared" si="3"/>
+        <v>129</v>
+      </c>
+      <c r="S44" s="15">
+        <f t="shared" si="2"/>
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="45" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N45" s="6">
+        <v>42</v>
+      </c>
+      <c r="O45" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P45" s="6">
+        <f t="shared" si="1"/>
+        <v>146</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>8</v>
+      </c>
+      <c r="R45" s="6">
+        <f t="shared" si="3"/>
+        <v>121</v>
+      </c>
+      <c r="S45" s="15">
+        <f t="shared" si="2"/>
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="46" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N46" s="6">
+        <v>43</v>
+      </c>
+      <c r="O46" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P46" s="6">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>10</v>
+      </c>
+      <c r="R46" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S46" s="15">
+        <f t="shared" si="2"/>
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="47" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N47" s="6">
+        <v>44</v>
+      </c>
+      <c r="O47" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P47" s="6">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>0</v>
+      </c>
+      <c r="R47" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S47" s="15">
+        <f t="shared" si="2"/>
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="48" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="N48" s="6">
+        <v>45</v>
+      </c>
+      <c r="O48" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P48" s="6">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>0</v>
+      </c>
+      <c r="R48" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S48" s="15">
+        <f t="shared" si="2"/>
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N49" s="6">
+        <v>46</v>
+      </c>
+      <c r="O49" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P49" s="6">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>0</v>
+      </c>
+      <c r="R49" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S49" s="15">
+        <f t="shared" si="2"/>
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N50" s="6">
+        <v>47</v>
+      </c>
+      <c r="O50" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P50" s="6">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0</v>
+      </c>
+      <c r="R50" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S50" s="15">
+        <f t="shared" si="2"/>
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="51" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N51" s="6">
+        <v>48</v>
+      </c>
+      <c r="O51" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P51" s="6">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0</v>
+      </c>
+      <c r="R51" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S51" s="15">
+        <f t="shared" si="2"/>
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="52" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N52" s="6">
+        <v>49</v>
+      </c>
+      <c r="O52" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P52" s="6">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>0</v>
+      </c>
+      <c r="R52" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S52" s="15">
+        <f t="shared" si="2"/>
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="53" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N53" s="6">
+        <v>50</v>
+      </c>
+      <c r="O53" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P53" s="6">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0</v>
+      </c>
+      <c r="R53" s="6">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="S53" s="15">
+        <f t="shared" si="2"/>
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="54" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N54" s="6">
+        <v>51</v>
+      </c>
+      <c r="O54" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P54" s="6">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>8</v>
+      </c>
+      <c r="R54" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S54" s="15">
+        <f t="shared" si="2"/>
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="55" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N55" s="6">
+        <v>52</v>
+      </c>
+      <c r="O55" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P55" s="6">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S55" s="15">
+        <f t="shared" si="2"/>
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="56" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N56" s="6">
+        <v>53</v>
+      </c>
+      <c r="O56" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P56" s="6">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S56" s="15">
+        <f t="shared" si="2"/>
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="57" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N57" s="6">
+        <v>54</v>
+      </c>
+      <c r="O57" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P57" s="6">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S57" s="15">
+        <f t="shared" si="2"/>
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="58" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N58" s="6">
+        <v>55</v>
+      </c>
+      <c r="O58" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P58" s="6">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S58" s="15">
+        <f t="shared" si="2"/>
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="59" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N59" s="6">
+        <v>56</v>
+      </c>
+      <c r="O59" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P59" s="6">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S59" s="15">
+        <f t="shared" si="2"/>
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="60" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N60" s="6">
+        <v>57</v>
+      </c>
+      <c r="O60" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P60" s="6">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S60" s="15">
+        <f t="shared" si="2"/>
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="61" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N61" s="6">
+        <v>58</v>
+      </c>
+      <c r="O61" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P61" s="6">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S61" s="15">
+        <f t="shared" si="2"/>
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="62" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N62" s="6">
+        <v>59</v>
+      </c>
+      <c r="O62" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P62" s="6">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S62" s="15">
+        <f t="shared" si="2"/>
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="63" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N63" s="6">
+        <v>60</v>
+      </c>
+      <c r="O63" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P63" s="6">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S63" s="15">
+        <f t="shared" si="2"/>
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="64" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N64" s="6">
+        <v>61</v>
+      </c>
+      <c r="O64" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P64" s="6">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S64" s="15">
+        <f t="shared" si="2"/>
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="65" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N65" s="6">
+        <v>62</v>
+      </c>
+      <c r="O65" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P65" s="6">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S65" s="15">
+        <f t="shared" si="2"/>
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="66" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N66" s="6">
+        <v>63</v>
+      </c>
+      <c r="O66" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P66" s="6">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S66" s="15">
+        <f t="shared" si="2"/>
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="67" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N67" s="6">
+        <v>64</v>
+      </c>
+      <c r="O67" s="29">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="P67" s="6">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S67" s="15">
+        <f t="shared" si="2"/>
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="68" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N68" s="6">
+        <v>65</v>
+      </c>
+      <c r="O68" s="29">
+        <f t="shared" ref="O68:O99" si="5">$B$10</f>
+        <v>3</v>
+      </c>
+      <c r="P68" s="6">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S68" s="15">
+        <f t="shared" si="2"/>
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="69" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N69" s="6">
+        <v>66</v>
+      </c>
+      <c r="O69" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P69" s="6">
+        <f t="shared" ref="P69:P117" si="6">P68-$O$4</f>
+        <v>74</v>
+      </c>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="S69" s="15">
+        <f t="shared" ref="S69:S117" si="7">S68+1</f>
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="70" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N70" s="6">
+        <v>67</v>
+      </c>
+      <c r="O70" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P70" s="6">
+        <f t="shared" si="6"/>
+        <v>71</v>
+      </c>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6">
+        <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
+        <v>103</v>
+      </c>
+      <c r="S70" s="15">
+        <f t="shared" si="7"/>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="71" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N71" s="6">
+        <v>68</v>
+      </c>
+      <c r="O71" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P71" s="6">
+        <f t="shared" si="6"/>
+        <v>68</v>
+      </c>
+      <c r="Q71" s="6"/>
+      <c r="R71" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S71" s="15">
+        <f t="shared" si="7"/>
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="72" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N72" s="6">
+        <v>69</v>
+      </c>
+      <c r="O72" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P72" s="6">
+        <f t="shared" si="6"/>
+        <v>65</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S72" s="15">
+        <f t="shared" si="7"/>
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="73" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N73" s="6">
+        <v>70</v>
+      </c>
+      <c r="O73" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P73" s="6">
+        <f t="shared" si="6"/>
+        <v>62</v>
+      </c>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S73" s="15">
+        <f t="shared" si="7"/>
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="74" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N74" s="6">
+        <v>71</v>
+      </c>
+      <c r="O74" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P74" s="6">
+        <f t="shared" si="6"/>
+        <v>59</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S74" s="15">
+        <f t="shared" si="7"/>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="75" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N75" s="6">
+        <v>72</v>
+      </c>
+      <c r="O75" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P75" s="6">
+        <f t="shared" si="6"/>
+        <v>56</v>
+      </c>
+      <c r="Q75" s="6"/>
+      <c r="R75" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S75" s="16">
+        <f t="shared" si="7"/>
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="76" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N76" s="6">
+        <v>73</v>
+      </c>
+      <c r="O76" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P76" s="6">
+        <f t="shared" si="6"/>
+        <v>53</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S76" s="16">
+        <f t="shared" si="7"/>
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="77" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N77" s="6">
+        <v>74</v>
+      </c>
+      <c r="O77" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P77" s="6">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="Q77" s="6"/>
+      <c r="R77" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S77" s="16">
+        <f t="shared" si="7"/>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="78" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N78" s="6">
+        <v>75</v>
+      </c>
+      <c r="O78" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P78" s="6">
+        <f t="shared" si="6"/>
+        <v>47</v>
+      </c>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S78" s="16">
+        <f t="shared" si="7"/>
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="79" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N79" s="6">
+        <v>76</v>
+      </c>
+      <c r="O79" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P79" s="6">
+        <f t="shared" si="6"/>
+        <v>44</v>
+      </c>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S79" s="16">
+        <f t="shared" si="7"/>
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="80" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N80" s="6">
+        <v>77</v>
+      </c>
+      <c r="O80" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P80" s="6">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S80" s="16">
+        <f t="shared" si="7"/>
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="81" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N81" s="6">
+        <v>78</v>
+      </c>
+      <c r="O81" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P81" s="6">
+        <f t="shared" si="6"/>
+        <v>38</v>
+      </c>
+      <c r="Q81" s="6"/>
+      <c r="R81" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S81" s="16">
+        <f t="shared" si="7"/>
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="82" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N82" s="6">
+        <v>79</v>
+      </c>
+      <c r="O82" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P82" s="6">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S82" s="16">
+        <f t="shared" si="7"/>
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="83" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N83" s="6">
+        <v>80</v>
+      </c>
+      <c r="O83" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P83" s="6">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="Q83" s="6"/>
+      <c r="R83" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S83" s="16">
+        <f t="shared" si="7"/>
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="84" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N84" s="6">
+        <v>81</v>
+      </c>
+      <c r="O84" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P84" s="6">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S84" s="16">
+        <f t="shared" si="7"/>
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="85" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N85" s="6">
+        <v>82</v>
+      </c>
+      <c r="O85" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P85" s="6">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q85" s="6"/>
+      <c r="R85" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S85" s="16">
+        <f t="shared" si="7"/>
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="86" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N86" s="6">
+        <v>83</v>
+      </c>
+      <c r="O86" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P86" s="6">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S86" s="16">
+        <f t="shared" si="7"/>
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="87" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N87" s="6">
+        <v>84</v>
+      </c>
+      <c r="O87" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P87" s="6">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="Q87" s="6"/>
+      <c r="R87" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S87" s="16">
+        <f t="shared" si="7"/>
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="88" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N88" s="6">
+        <v>85</v>
+      </c>
+      <c r="O88" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P88" s="6">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S88" s="16">
+        <f t="shared" si="7"/>
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="89" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N89" s="6">
+        <v>86</v>
+      </c>
+      <c r="O89" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P89" s="6">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="Q89" s="6"/>
+      <c r="R89" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S89" s="16">
+        <f t="shared" si="7"/>
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="90" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N90" s="6">
+        <v>87</v>
+      </c>
+      <c r="O90" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P90" s="6">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S90" s="16">
+        <f t="shared" si="7"/>
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="91" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N91" s="6">
+        <v>88</v>
+      </c>
+      <c r="O91" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P91" s="6">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S91" s="16">
+        <f t="shared" si="7"/>
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="92" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N92" s="6">
+        <v>89</v>
+      </c>
+      <c r="O92" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P92" s="6">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S92" s="16">
+        <f t="shared" si="7"/>
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="93" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N93" s="6">
+        <v>90</v>
+      </c>
+      <c r="O93" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P93" s="6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="Q93" s="6"/>
+      <c r="R93" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S93" s="16">
+        <f t="shared" si="7"/>
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="94" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N94" s="6">
+        <v>91</v>
+      </c>
+      <c r="O94" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P94" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S94" s="16">
+        <f t="shared" si="7"/>
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="95" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N95" s="6">
+        <v>92</v>
+      </c>
+      <c r="O95" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P95" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="6"/>
+      <c r="R95" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S95" s="16">
+        <f t="shared" si="7"/>
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="96" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N96" s="6">
+        <v>93</v>
+      </c>
+      <c r="O96" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P96" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S96" s="16">
+        <f t="shared" si="7"/>
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="97" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N97" s="6">
+        <v>94</v>
+      </c>
+      <c r="O97" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P97" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S97" s="16">
+        <f t="shared" si="7"/>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="98" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N98" s="6">
+        <v>95</v>
+      </c>
+      <c r="O98" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P98" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S98" s="16">
+        <f t="shared" si="7"/>
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="99" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N99" s="6">
+        <v>96</v>
+      </c>
+      <c r="O99" s="29">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="P99" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S99" s="16">
+        <f t="shared" si="7"/>
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="100" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N100" s="6">
+        <v>97</v>
+      </c>
+      <c r="O100" s="29">
+        <f t="shared" ref="O100:O117" si="9">$B$10</f>
+        <v>3</v>
+      </c>
+      <c r="P100" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S100" s="16">
+        <f t="shared" si="7"/>
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="101" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N101" s="6">
+        <v>98</v>
+      </c>
+      <c r="O101" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P101" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S101" s="16">
+        <f t="shared" si="7"/>
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="102" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N102" s="6">
+        <v>99</v>
+      </c>
+      <c r="O102" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P102" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S102" s="16">
+        <f t="shared" si="7"/>
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="103" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N103" s="6">
+        <v>100</v>
+      </c>
+      <c r="O103" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P103" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="6"/>
+      <c r="R103" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S103" s="16">
+        <f t="shared" si="7"/>
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="104" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N104" s="6">
+        <v>101</v>
+      </c>
+      <c r="O104" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P104" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S104" s="16">
+        <f t="shared" si="7"/>
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="105" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N105" s="6">
+        <v>102</v>
+      </c>
+      <c r="O105" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P105" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="6"/>
+      <c r="R105" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S105" s="16">
+        <f t="shared" si="7"/>
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="106" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N106" s="6">
+        <v>103</v>
+      </c>
+      <c r="O106" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P106" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S106" s="16">
+        <f t="shared" si="7"/>
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="107" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N107" s="6">
+        <v>104</v>
+      </c>
+      <c r="O107" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P107" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="6"/>
+      <c r="R107" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S107" s="16">
+        <f t="shared" si="7"/>
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="108" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N108" s="6">
+        <v>105</v>
+      </c>
+      <c r="O108" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P108" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S108" s="16">
+        <f t="shared" si="7"/>
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="109" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N109" s="6">
+        <v>106</v>
+      </c>
+      <c r="O109" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P109" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S109" s="16">
+        <f t="shared" si="7"/>
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="110" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N110" s="6">
+        <v>107</v>
+      </c>
+      <c r="O110" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P110" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S110" s="16">
+        <f t="shared" si="7"/>
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="111" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N111" s="6">
+        <v>108</v>
+      </c>
+      <c r="O111" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P111" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="6"/>
+      <c r="R111" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S111" s="16">
+        <f t="shared" si="7"/>
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="112" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N112" s="6">
+        <v>109</v>
+      </c>
+      <c r="O112" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P112" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S112" s="16">
+        <f t="shared" si="7"/>
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="113" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N113" s="6">
+        <v>110</v>
+      </c>
+      <c r="O113" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P113" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S113" s="16">
+        <f t="shared" si="7"/>
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="114" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N114" s="6">
+        <v>111</v>
+      </c>
+      <c r="O114" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P114" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S114" s="16">
+        <f t="shared" si="7"/>
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="115" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N115" s="6">
+        <v>112</v>
+      </c>
+      <c r="O115" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P115" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S115" s="16">
+        <f t="shared" si="7"/>
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="116" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N116" s="6">
+        <v>113</v>
+      </c>
+      <c r="O116" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P116" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S116" s="16">
+        <f t="shared" si="7"/>
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="117" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="N117" s="6">
+        <v>114</v>
+      </c>
+      <c r="O117" s="29">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="P117" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="6"/>
+      <c r="R117" s="6">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S117" s="16">
+        <f t="shared" si="7"/>
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="118" spans="14:19" x14ac:dyDescent="0.25">
+      <c r="S118" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="N3:N117">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P117">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:Q117">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:R117">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -5,19 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albuq\Repositorios\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BBD663-2B8F-404B-A035-3EA7C7743808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F99A68F-2191-4E2A-BE6E-76473101E5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="120">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -409,6 +406,18 @@
   </si>
   <si>
     <t>10/02/26 - 03/06/26</t>
+  </si>
+  <si>
+    <t>Dashboard intregado com o Bd</t>
+  </si>
+  <si>
+    <t>Desenvolver uma dashboard integrado ao Banco de Dados</t>
+  </si>
+  <si>
+    <t>Site de login com CRUD</t>
+  </si>
+  <si>
+    <t>Desenvolver um site de login sendo póssivel CRUD</t>
   </si>
 </sst>
 </file>
@@ -536,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -596,11 +605,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -681,9 +703,48 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2423,15 +2484,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>599515</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>169208</xdr:rowOff>
+      <xdr:colOff>420222</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>158002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>997323</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>11206</xdr:rowOff>
+      <xdr:colOff>818030</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2457,372 +2518,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Planilha1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="N1" t="str">
-            <v>Meta Ideal</v>
-          </cell>
-          <cell r="O1" t="str">
-            <v>Pendente</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="M2">
-            <v>0</v>
-          </cell>
-          <cell r="N2">
-            <v>360</v>
-          </cell>
-          <cell r="O2">
-            <v>370</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="M3">
-            <v>1</v>
-          </cell>
-          <cell r="N3">
-            <v>348</v>
-          </cell>
-          <cell r="O3">
-            <v>358</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="M4">
-            <v>2</v>
-          </cell>
-          <cell r="N4">
-            <v>336</v>
-          </cell>
-          <cell r="O4">
-            <v>346</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="M5">
-            <v>3</v>
-          </cell>
-          <cell r="N5">
-            <v>324</v>
-          </cell>
-          <cell r="O5">
-            <v>334</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="M6">
-            <v>4</v>
-          </cell>
-          <cell r="N6">
-            <v>312</v>
-          </cell>
-          <cell r="O6">
-            <v>322</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="M7">
-            <v>5</v>
-          </cell>
-          <cell r="N7">
-            <v>300</v>
-          </cell>
-          <cell r="O7">
-            <v>310</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="M8">
-            <v>6</v>
-          </cell>
-          <cell r="N8">
-            <v>288</v>
-          </cell>
-          <cell r="O8">
-            <v>298</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="M9">
-            <v>7</v>
-          </cell>
-          <cell r="N9">
-            <v>276</v>
-          </cell>
-          <cell r="O9">
-            <v>286</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="M10">
-            <v>8</v>
-          </cell>
-          <cell r="N10">
-            <v>264</v>
-          </cell>
-          <cell r="O10">
-            <v>274</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="M11">
-            <v>9</v>
-          </cell>
-          <cell r="N11">
-            <v>252</v>
-          </cell>
-          <cell r="O11">
-            <v>262</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="M12">
-            <v>10</v>
-          </cell>
-          <cell r="N12">
-            <v>240</v>
-          </cell>
-          <cell r="O12">
-            <v>240</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="M13">
-            <v>11</v>
-          </cell>
-          <cell r="N13">
-            <v>228</v>
-          </cell>
-          <cell r="O13">
-            <v>228</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="M14">
-            <v>12</v>
-          </cell>
-          <cell r="N14">
-            <v>216</v>
-          </cell>
-          <cell r="O14">
-            <v>216</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="M15">
-            <v>13</v>
-          </cell>
-          <cell r="N15">
-            <v>204</v>
-          </cell>
-          <cell r="O15">
-            <v>204</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="M16">
-            <v>14</v>
-          </cell>
-          <cell r="N16">
-            <v>192</v>
-          </cell>
-          <cell r="O16">
-            <v>192</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="M17">
-            <v>15</v>
-          </cell>
-          <cell r="N17">
-            <v>180</v>
-          </cell>
-          <cell r="O17">
-            <v>180</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="M18">
-            <v>16</v>
-          </cell>
-          <cell r="N18">
-            <v>168</v>
-          </cell>
-          <cell r="O18">
-            <v>168</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="M19">
-            <v>17</v>
-          </cell>
-          <cell r="N19">
-            <v>156</v>
-          </cell>
-          <cell r="O19">
-            <v>156</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="M20">
-            <v>18</v>
-          </cell>
-          <cell r="N20">
-            <v>144</v>
-          </cell>
-          <cell r="O20">
-            <v>144</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="M21">
-            <v>19</v>
-          </cell>
-          <cell r="N21">
-            <v>132</v>
-          </cell>
-          <cell r="O21">
-            <v>132</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="M22">
-            <v>20</v>
-          </cell>
-          <cell r="N22">
-            <v>120</v>
-          </cell>
-          <cell r="O22">
-            <v>120</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="M23">
-            <v>21</v>
-          </cell>
-          <cell r="N23">
-            <v>108</v>
-          </cell>
-          <cell r="O23">
-            <v>98</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="M24">
-            <v>22</v>
-          </cell>
-          <cell r="N24">
-            <v>96</v>
-          </cell>
-          <cell r="O24">
-            <v>86</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="M25">
-            <v>23</v>
-          </cell>
-          <cell r="N25">
-            <v>84</v>
-          </cell>
-          <cell r="O25">
-            <v>74</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="M26">
-            <v>24</v>
-          </cell>
-          <cell r="N26">
-            <v>72</v>
-          </cell>
-          <cell r="O26">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="M27">
-            <v>25</v>
-          </cell>
-          <cell r="N27">
-            <v>60</v>
-          </cell>
-          <cell r="O27">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="M28">
-            <v>26</v>
-          </cell>
-          <cell r="N28">
-            <v>48</v>
-          </cell>
-          <cell r="O28">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="M29">
-            <v>27</v>
-          </cell>
-          <cell r="N29">
-            <v>36</v>
-          </cell>
-          <cell r="O29">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="M30">
-            <v>28</v>
-          </cell>
-          <cell r="N30">
-            <v>24</v>
-          </cell>
-          <cell r="O30">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="M31">
-            <v>29</v>
-          </cell>
-          <cell r="N31">
-            <v>12</v>
-          </cell>
-          <cell r="O31">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="M32">
-            <v>30</v>
-          </cell>
-          <cell r="N32">
-            <v>0</v>
-          </cell>
-          <cell r="O32">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4991,28 +4686,28 @@
       </c>
     </row>
     <row r="39" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="H39" s="25" t="s">
+      <c r="H39" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="35">
         <v>8</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="36">
         <v>2</v>
       </c>
-      <c r="K39" s="28" t="s">
+      <c r="K39" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="L39" s="4"/>
+      <c r="L39" s="38"/>
       <c r="N39" s="6">
         <v>36</v>
       </c>
@@ -5037,6 +4732,28 @@
       </c>
     </row>
     <row r="40" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E40" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="I40" s="41">
+        <v>21</v>
+      </c>
+      <c r="J40" s="12">
+        <v>1</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L40" s="39"/>
       <c r="N40" s="6">
         <v>37</v>
       </c>
@@ -5061,6 +4778,28 @@
       </c>
     </row>
     <row r="41" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E41" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" s="44">
+        <v>13</v>
+      </c>
+      <c r="J41" s="45">
+        <v>2</v>
+      </c>
+      <c r="K41" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="L41" s="42"/>
       <c r="N41" s="6">
         <v>38</v>
       </c>
@@ -5157,6 +4896,7 @@
       </c>
     </row>
     <row r="45" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="G45" s="47"/>
       <c r="N45" s="6">
         <v>42</v>
       </c>
@@ -5713,7 +5453,7 @@
         <v>3</v>
       </c>
       <c r="P69" s="6">
-        <f t="shared" ref="P69:P117" si="6">P68-$O$4</f>
+        <f t="shared" ref="P69:P93" si="6">P68-$O$4</f>
         <v>74</v>
       </c>
       <c r="Q69" s="6"/>
@@ -6764,14 +6504,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="N3:N117">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -6780,6 +6512,14 @@
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albuq\Repositorios\ThermoChain\Documentações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F99A68F-2191-4E2A-BE6E-76473101E5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9043B5DC-6179-4972-B9FC-F6B2F63B3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -622,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -731,20 +731,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,10 +1245,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$R$3:$R$117</c:f>
+              <c:f>Planilha1!$R$3:$R$58</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="115"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>272</c:v>
                 </c:pt>
@@ -1423,184 +1415,7 @@
                   <c:v>103</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>103</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2838,29 +2653,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
   <dimension ref="A2:T118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" customWidth="1"/>
-    <col min="6" max="6" width="53.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" customWidth="1"/>
+    <col min="6" max="6" width="53.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" customWidth="1"/>
+    <col min="19" max="19" width="13.88671875" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>59</v>
       </c>
@@ -2913,7 +2728,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
@@ -2968,7 +2783,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>60</v>
       </c>
@@ -3026,7 +2841,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>61</v>
       </c>
@@ -3083,7 +2898,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>64</v>
       </c>
@@ -3137,7 +2952,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E7" s="19" t="s">
         <v>4</v>
       </c>
@@ -3185,7 +3000,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>101</v>
       </c>
@@ -3240,7 +3055,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>102</v>
       </c>
@@ -3294,7 +3109,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
@@ -3349,7 +3164,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>114</v>
       </c>
@@ -3403,7 +3218,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E12" s="19" t="s">
         <v>9</v>
       </c>
@@ -3451,7 +3266,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="E13" s="19" t="s">
         <v>10</v>
@@ -3500,7 +3315,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="E14" s="19" t="s">
         <v>11</v>
@@ -3549,7 +3364,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E15" s="19" t="s">
         <v>12</v>
       </c>
@@ -3597,7 +3412,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
@@ -3645,7 +3460,7 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E17" s="19" t="s">
         <v>14</v>
       </c>
@@ -3693,7 +3508,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E18" s="19" t="s">
         <v>15</v>
       </c>
@@ -3741,7 +3556,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
@@ -3789,7 +3604,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
@@ -3835,7 +3650,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E21" s="19" t="s">
         <v>26</v>
       </c>
@@ -3883,11 +3698,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="17" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="20" t="s">
@@ -3931,7 +3746,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E23" s="19" t="s">
         <v>28</v>
       </c>
@@ -3979,7 +3794,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E24" s="19" t="s">
         <v>29</v>
       </c>
@@ -4027,7 +3842,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E25" s="19" t="s">
         <v>30</v>
       </c>
@@ -4073,7 +3888,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E26" s="19" t="s">
         <v>31</v>
       </c>
@@ -4121,7 +3936,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
@@ -4169,7 +3984,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E28" s="19" t="s">
         <v>33</v>
       </c>
@@ -4217,7 +4032,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E29" s="19" t="s">
         <v>34</v>
       </c>
@@ -4265,7 +4080,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E30" s="19" t="s">
         <v>35</v>
       </c>
@@ -4313,7 +4128,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E31" s="19" t="s">
         <v>36</v>
       </c>
@@ -4359,7 +4174,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E32" s="19" t="s">
         <v>37</v>
       </c>
@@ -4407,7 +4222,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E33" s="19" t="s">
         <v>38</v>
       </c>
@@ -4455,7 +4270,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="34" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
@@ -4501,7 +4316,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E35" s="19" t="s">
         <v>90</v>
       </c>
@@ -4547,7 +4362,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="36" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E36" s="19" t="s">
         <v>91</v>
       </c>
@@ -4593,7 +4408,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="37" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E37" s="19" t="s">
         <v>92</v>
       </c>
@@ -4639,7 +4454,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E38" s="19" t="s">
         <v>93</v>
       </c>
@@ -4685,7 +4500,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="39" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E39" s="31" t="s">
         <v>94</v>
       </c>
@@ -4731,7 +4546,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="40" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E40" s="32" t="s">
         <v>116</v>
       </c>
@@ -4777,29 +4592,29 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="41" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E41" s="42" t="s">
+    <row r="41" spans="5:19" x14ac:dyDescent="0.3">
+      <c r="E41" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="F41" s="42" t="s">
+      <c r="F41" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="G41" s="43" t="s">
+      <c r="G41" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="42">
         <v>13</v>
       </c>
-      <c r="J41" s="45">
+      <c r="J41" s="43">
         <v>2</v>
       </c>
-      <c r="K41" s="46" t="s">
+      <c r="K41" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L41" s="42"/>
+      <c r="L41" s="39"/>
       <c r="N41" s="6">
         <v>38</v>
       </c>
@@ -4823,7 +4638,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="42" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N42" s="6">
         <v>39</v>
       </c>
@@ -4847,7 +4662,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="43" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N43" s="6">
         <v>40</v>
       </c>
@@ -4871,7 +4686,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="44" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N44" s="6">
         <v>41</v>
       </c>
@@ -4895,8 +4710,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="45" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="G45" s="47"/>
+    <row r="45" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N45" s="6">
         <v>42</v>
       </c>
@@ -4920,7 +4734,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="46" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N46" s="6">
         <v>43</v>
       </c>
@@ -4944,7 +4758,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="47" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N47" s="6">
         <v>44</v>
       </c>
@@ -4968,7 +4782,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="48" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N48" s="6">
         <v>45</v>
       </c>
@@ -4992,7 +4806,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N49" s="6">
         <v>46</v>
       </c>
@@ -5016,7 +4830,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N50" s="6">
         <v>47</v>
       </c>
@@ -5040,7 +4854,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="51" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N51" s="6">
         <v>48</v>
       </c>
@@ -5064,7 +4878,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="52" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N52" s="6">
         <v>49</v>
       </c>
@@ -5088,7 +4902,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="53" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N53" s="6">
         <v>50</v>
       </c>
@@ -5112,7 +4926,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="54" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N54" s="6">
         <v>51</v>
       </c>
@@ -5136,7 +4950,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="55" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N55" s="6">
         <v>52</v>
       </c>
@@ -5148,7 +4962,9 @@
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
-      <c r="Q55" s="6"/>
+      <c r="Q55" s="6">
+        <v>0</v>
+      </c>
       <c r="R55" s="6">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -5158,7 +4974,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="56" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N56" s="6">
         <v>53</v>
       </c>
@@ -5170,7 +4986,9 @@
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
-      <c r="Q56" s="6"/>
+      <c r="Q56" s="6">
+        <v>0</v>
+      </c>
       <c r="R56" s="6">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -5180,7 +4998,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="57" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N57" s="6">
         <v>54</v>
       </c>
@@ -5192,7 +5010,9 @@
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="Q57" s="6"/>
+      <c r="Q57" s="6">
+        <v>0</v>
+      </c>
       <c r="R57" s="6">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -5202,7 +5022,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="58" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N58" s="6">
         <v>55</v>
       </c>
@@ -5214,17 +5034,19 @@
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
-      <c r="Q58" s="6"/>
+      <c r="Q58" s="6">
+        <v>13</v>
+      </c>
       <c r="R58" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S58" s="15">
         <f t="shared" si="2"/>
         <v>46118</v>
       </c>
     </row>
-    <row r="59" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N59" s="6">
         <v>56</v>
       </c>
@@ -5239,14 +5061,14 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S59" s="15">
         <f t="shared" si="2"/>
         <v>46119</v>
       </c>
     </row>
-    <row r="60" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N60" s="6">
         <v>57</v>
       </c>
@@ -5261,14 +5083,14 @@
       <c r="Q60" s="6"/>
       <c r="R60" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S60" s="15">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
     </row>
-    <row r="61" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N61" s="6">
         <v>58</v>
       </c>
@@ -5283,14 +5105,14 @@
       <c r="Q61" s="6"/>
       <c r="R61" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S61" s="15">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
     </row>
-    <row r="62" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N62" s="6">
         <v>59</v>
       </c>
@@ -5305,14 +5127,14 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S62" s="15">
         <f t="shared" si="2"/>
         <v>46122</v>
       </c>
     </row>
-    <row r="63" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N63" s="6">
         <v>60</v>
       </c>
@@ -5327,14 +5149,14 @@
       <c r="Q63" s="6"/>
       <c r="R63" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S63" s="15">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
     </row>
-    <row r="64" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N64" s="6">
         <v>61</v>
       </c>
@@ -5349,14 +5171,14 @@
       <c r="Q64" s="6"/>
       <c r="R64" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S64" s="15">
         <f t="shared" si="2"/>
         <v>46124</v>
       </c>
     </row>
-    <row r="65" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N65" s="6">
         <v>62</v>
       </c>
@@ -5371,14 +5193,14 @@
       <c r="Q65" s="6"/>
       <c r="R65" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S65" s="15">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
     </row>
-    <row r="66" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N66" s="6">
         <v>63</v>
       </c>
@@ -5393,14 +5215,14 @@
       <c r="Q66" s="6"/>
       <c r="R66" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S66" s="15">
         <f t="shared" si="2"/>
         <v>46126</v>
       </c>
     </row>
-    <row r="67" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N67" s="6">
         <v>64</v>
       </c>
@@ -5415,14 +5237,14 @@
       <c r="Q67" s="6"/>
       <c r="R67" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S67" s="15">
         <f t="shared" si="2"/>
         <v>46127</v>
       </c>
     </row>
-    <row r="68" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N68" s="6">
         <v>65</v>
       </c>
@@ -5437,14 +5259,14 @@
       <c r="Q68" s="6"/>
       <c r="R68" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S68" s="15">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
     </row>
-    <row r="69" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N69" s="6">
         <v>66</v>
       </c>
@@ -5459,14 +5281,14 @@
       <c r="Q69" s="6"/>
       <c r="R69" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S69" s="15">
         <f t="shared" ref="S69:S117" si="7">S68+1</f>
         <v>46129</v>
       </c>
     </row>
-    <row r="70" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N70" s="6">
         <v>67</v>
       </c>
@@ -5481,14 +5303,14 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6">
         <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S70" s="15">
         <f t="shared" si="7"/>
         <v>46130</v>
       </c>
     </row>
-    <row r="71" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N71" s="6">
         <v>68</v>
       </c>
@@ -5503,14 +5325,14 @@
       <c r="Q71" s="6"/>
       <c r="R71" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S71" s="15">
         <f t="shared" si="7"/>
         <v>46131</v>
       </c>
     </row>
-    <row r="72" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N72" s="6">
         <v>69</v>
       </c>
@@ -5525,14 +5347,14 @@
       <c r="Q72" s="6"/>
       <c r="R72" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S72" s="15">
         <f t="shared" si="7"/>
         <v>46132</v>
       </c>
     </row>
-    <row r="73" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N73" s="6">
         <v>70</v>
       </c>
@@ -5547,14 +5369,14 @@
       <c r="Q73" s="6"/>
       <c r="R73" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S73" s="15">
         <f t="shared" si="7"/>
         <v>46133</v>
       </c>
     </row>
-    <row r="74" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N74" s="6">
         <v>71</v>
       </c>
@@ -5569,14 +5391,14 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S74" s="15">
         <f t="shared" si="7"/>
         <v>46134</v>
       </c>
     </row>
-    <row r="75" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N75" s="6">
         <v>72</v>
       </c>
@@ -5591,14 +5413,14 @@
       <c r="Q75" s="6"/>
       <c r="R75" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S75" s="16">
         <f t="shared" si="7"/>
         <v>46135</v>
       </c>
     </row>
-    <row r="76" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N76" s="6">
         <v>73</v>
       </c>
@@ -5613,14 +5435,14 @@
       <c r="Q76" s="6"/>
       <c r="R76" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S76" s="16">
         <f t="shared" si="7"/>
         <v>46136</v>
       </c>
     </row>
-    <row r="77" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N77" s="6">
         <v>74</v>
       </c>
@@ -5635,14 +5457,14 @@
       <c r="Q77" s="6"/>
       <c r="R77" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S77" s="16">
         <f t="shared" si="7"/>
         <v>46137</v>
       </c>
     </row>
-    <row r="78" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N78" s="6">
         <v>75</v>
       </c>
@@ -5657,14 +5479,14 @@
       <c r="Q78" s="6"/>
       <c r="R78" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S78" s="16">
         <f t="shared" si="7"/>
         <v>46138</v>
       </c>
     </row>
-    <row r="79" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N79" s="6">
         <v>76</v>
       </c>
@@ -5679,14 +5501,14 @@
       <c r="Q79" s="6"/>
       <c r="R79" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S79" s="16">
         <f t="shared" si="7"/>
         <v>46139</v>
       </c>
     </row>
-    <row r="80" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N80" s="6">
         <v>77</v>
       </c>
@@ -5701,14 +5523,14 @@
       <c r="Q80" s="6"/>
       <c r="R80" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S80" s="16">
         <f t="shared" si="7"/>
         <v>46140</v>
       </c>
     </row>
-    <row r="81" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N81" s="6">
         <v>78</v>
       </c>
@@ -5723,14 +5545,14 @@
       <c r="Q81" s="6"/>
       <c r="R81" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S81" s="16">
         <f t="shared" si="7"/>
         <v>46141</v>
       </c>
     </row>
-    <row r="82" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N82" s="6">
         <v>79</v>
       </c>
@@ -5745,14 +5567,14 @@
       <c r="Q82" s="6"/>
       <c r="R82" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S82" s="16">
         <f t="shared" si="7"/>
         <v>46142</v>
       </c>
     </row>
-    <row r="83" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N83" s="6">
         <v>80</v>
       </c>
@@ -5767,14 +5589,14 @@
       <c r="Q83" s="6"/>
       <c r="R83" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S83" s="16">
         <f t="shared" si="7"/>
         <v>46143</v>
       </c>
     </row>
-    <row r="84" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N84" s="6">
         <v>81</v>
       </c>
@@ -5789,14 +5611,14 @@
       <c r="Q84" s="6"/>
       <c r="R84" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S84" s="16">
         <f t="shared" si="7"/>
         <v>46144</v>
       </c>
     </row>
-    <row r="85" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N85" s="6">
         <v>82</v>
       </c>
@@ -5811,14 +5633,14 @@
       <c r="Q85" s="6"/>
       <c r="R85" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S85" s="16">
         <f t="shared" si="7"/>
         <v>46145</v>
       </c>
     </row>
-    <row r="86" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N86" s="6">
         <v>83</v>
       </c>
@@ -5833,14 +5655,14 @@
       <c r="Q86" s="6"/>
       <c r="R86" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S86" s="16">
         <f t="shared" si="7"/>
         <v>46146</v>
       </c>
     </row>
-    <row r="87" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N87" s="6">
         <v>84</v>
       </c>
@@ -5855,14 +5677,14 @@
       <c r="Q87" s="6"/>
       <c r="R87" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S87" s="16">
         <f t="shared" si="7"/>
         <v>46147</v>
       </c>
     </row>
-    <row r="88" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N88" s="6">
         <v>85</v>
       </c>
@@ -5877,14 +5699,14 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S88" s="16">
         <f t="shared" si="7"/>
         <v>46148</v>
       </c>
     </row>
-    <row r="89" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N89" s="6">
         <v>86</v>
       </c>
@@ -5899,14 +5721,14 @@
       <c r="Q89" s="6"/>
       <c r="R89" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S89" s="16">
         <f t="shared" si="7"/>
         <v>46149</v>
       </c>
     </row>
-    <row r="90" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N90" s="6">
         <v>87</v>
       </c>
@@ -5921,14 +5743,14 @@
       <c r="Q90" s="6"/>
       <c r="R90" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S90" s="16">
         <f t="shared" si="7"/>
         <v>46150</v>
       </c>
     </row>
-    <row r="91" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N91" s="6">
         <v>88</v>
       </c>
@@ -5943,14 +5765,14 @@
       <c r="Q91" s="6"/>
       <c r="R91" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S91" s="16">
         <f t="shared" si="7"/>
         <v>46151</v>
       </c>
     </row>
-    <row r="92" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N92" s="6">
         <v>89</v>
       </c>
@@ -5965,14 +5787,14 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S92" s="16">
         <f t="shared" si="7"/>
         <v>46152</v>
       </c>
     </row>
-    <row r="93" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N93" s="6">
         <v>90</v>
       </c>
@@ -5987,14 +5809,14 @@
       <c r="Q93" s="6"/>
       <c r="R93" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S93" s="16">
         <f t="shared" si="7"/>
         <v>46153</v>
       </c>
     </row>
-    <row r="94" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N94" s="6">
         <v>91</v>
       </c>
@@ -6008,14 +5830,14 @@
       <c r="Q94" s="6"/>
       <c r="R94" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S94" s="16">
         <f t="shared" si="7"/>
         <v>46154</v>
       </c>
     </row>
-    <row r="95" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N95" s="6">
         <v>92</v>
       </c>
@@ -6029,14 +5851,14 @@
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S95" s="16">
         <f t="shared" si="7"/>
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N96" s="6">
         <v>93</v>
       </c>
@@ -6050,14 +5872,14 @@
       <c r="Q96" s="6"/>
       <c r="R96" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S96" s="16">
         <f t="shared" si="7"/>
         <v>46156</v>
       </c>
     </row>
-    <row r="97" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N97" s="6">
         <v>94</v>
       </c>
@@ -6071,14 +5893,14 @@
       <c r="Q97" s="6"/>
       <c r="R97" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S97" s="16">
         <f t="shared" si="7"/>
         <v>46157</v>
       </c>
     </row>
-    <row r="98" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N98" s="6">
         <v>95</v>
       </c>
@@ -6092,14 +5914,14 @@
       <c r="Q98" s="6"/>
       <c r="R98" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S98" s="16">
         <f t="shared" si="7"/>
         <v>46158</v>
       </c>
     </row>
-    <row r="99" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N99" s="6">
         <v>96</v>
       </c>
@@ -6113,14 +5935,14 @@
       <c r="Q99" s="6"/>
       <c r="R99" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S99" s="16">
         <f t="shared" si="7"/>
         <v>46159</v>
       </c>
     </row>
-    <row r="100" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N100" s="6">
         <v>97</v>
       </c>
@@ -6134,14 +5956,14 @@
       <c r="Q100" s="6"/>
       <c r="R100" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S100" s="16">
         <f t="shared" si="7"/>
         <v>46160</v>
       </c>
     </row>
-    <row r="101" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N101" s="6">
         <v>98</v>
       </c>
@@ -6155,14 +5977,14 @@
       <c r="Q101" s="6"/>
       <c r="R101" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S101" s="16">
         <f t="shared" si="7"/>
         <v>46161</v>
       </c>
     </row>
-    <row r="102" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N102" s="6">
         <v>99</v>
       </c>
@@ -6176,14 +5998,14 @@
       <c r="Q102" s="6"/>
       <c r="R102" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S102" s="16">
         <f t="shared" si="7"/>
         <v>46162</v>
       </c>
     </row>
-    <row r="103" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N103" s="6">
         <v>100</v>
       </c>
@@ -6197,14 +6019,14 @@
       <c r="Q103" s="6"/>
       <c r="R103" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S103" s="16">
         <f t="shared" si="7"/>
         <v>46163</v>
       </c>
     </row>
-    <row r="104" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N104" s="6">
         <v>101</v>
       </c>
@@ -6218,14 +6040,14 @@
       <c r="Q104" s="6"/>
       <c r="R104" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S104" s="16">
         <f t="shared" si="7"/>
         <v>46164</v>
       </c>
     </row>
-    <row r="105" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N105" s="6">
         <v>102</v>
       </c>
@@ -6239,14 +6061,14 @@
       <c r="Q105" s="6"/>
       <c r="R105" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S105" s="16">
         <f t="shared" si="7"/>
         <v>46165</v>
       </c>
     </row>
-    <row r="106" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N106" s="6">
         <v>103</v>
       </c>
@@ -6260,14 +6082,14 @@
       <c r="Q106" s="6"/>
       <c r="R106" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S106" s="16">
         <f t="shared" si="7"/>
         <v>46166</v>
       </c>
     </row>
-    <row r="107" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N107" s="6">
         <v>104</v>
       </c>
@@ -6281,14 +6103,14 @@
       <c r="Q107" s="6"/>
       <c r="R107" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S107" s="16">
         <f t="shared" si="7"/>
         <v>46167</v>
       </c>
     </row>
-    <row r="108" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N108" s="6">
         <v>105</v>
       </c>
@@ -6302,14 +6124,14 @@
       <c r="Q108" s="6"/>
       <c r="R108" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S108" s="16">
         <f t="shared" si="7"/>
         <v>46168</v>
       </c>
     </row>
-    <row r="109" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N109" s="6">
         <v>106</v>
       </c>
@@ -6323,14 +6145,14 @@
       <c r="Q109" s="6"/>
       <c r="R109" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S109" s="16">
         <f t="shared" si="7"/>
         <v>46169</v>
       </c>
     </row>
-    <row r="110" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N110" s="6">
         <v>107</v>
       </c>
@@ -6344,14 +6166,14 @@
       <c r="Q110" s="6"/>
       <c r="R110" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S110" s="16">
         <f t="shared" si="7"/>
         <v>46170</v>
       </c>
     </row>
-    <row r="111" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N111" s="6">
         <v>108</v>
       </c>
@@ -6365,14 +6187,14 @@
       <c r="Q111" s="6"/>
       <c r="R111" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S111" s="16">
         <f t="shared" si="7"/>
         <v>46171</v>
       </c>
     </row>
-    <row r="112" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N112" s="6">
         <v>109</v>
       </c>
@@ -6386,14 +6208,14 @@
       <c r="Q112" s="6"/>
       <c r="R112" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S112" s="16">
         <f t="shared" si="7"/>
         <v>46172</v>
       </c>
     </row>
-    <row r="113" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N113" s="6">
         <v>110</v>
       </c>
@@ -6407,14 +6229,14 @@
       <c r="Q113" s="6"/>
       <c r="R113" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S113" s="16">
         <f t="shared" si="7"/>
         <v>46173</v>
       </c>
     </row>
-    <row r="114" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N114" s="6">
         <v>111</v>
       </c>
@@ -6428,14 +6250,14 @@
       <c r="Q114" s="6"/>
       <c r="R114" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S114" s="16">
         <f t="shared" si="7"/>
         <v>46174</v>
       </c>
     </row>
-    <row r="115" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N115" s="6">
         <v>112</v>
       </c>
@@ -6449,14 +6271,14 @@
       <c r="Q115" s="6"/>
       <c r="R115" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S115" s="16">
         <f t="shared" si="7"/>
         <v>46175</v>
       </c>
     </row>
-    <row r="116" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N116" s="6">
         <v>113</v>
       </c>
@@ -6470,14 +6292,14 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S116" s="16">
         <f t="shared" si="7"/>
         <v>46176</v>
       </c>
     </row>
-    <row r="117" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N117" s="6">
         <v>114</v>
       </c>
@@ -6491,14 +6313,14 @@
       <c r="Q117" s="6"/>
       <c r="R117" s="6">
         <f t="shared" si="8"/>
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="S117" s="16">
         <f t="shared" si="7"/>
         <v>46177</v>
       </c>
     </row>
-    <row r="118" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="14:19" x14ac:dyDescent="0.3">
       <c r="S118" s="5"/>
     </row>
   </sheetData>

--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9043B5DC-6179-4972-B9FC-F6B2F63B3114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9158A729-86B7-43D7-98AC-F1DF5A4FB052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint01" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint02" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="120">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -860,7 +862,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$P$3:$P$117</c:f>
+              <c:f>Backlog!$P$3:$P$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="115"/>
@@ -1223,7 +1225,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Pendente</c:v>
+            <c:strRef>
+              <c:f>Backlog!$R$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="34925" cap="rnd">
@@ -1245,10 +1255,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$R$3:$R$58</c:f>
+              <c:f>Backlog!$R$3:$R$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>272</c:v>
                 </c:pt>
@@ -1415,6 +1425,18 @@
                   <c:v>103</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>90</c:v>
                 </c:pt>
               </c:numCache>
@@ -1515,6 +1537,7 @@
             </a:p>
           </c:txPr>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2653,29 +2676,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
   <dimension ref="A2:T118"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="5" max="5" width="45.6640625" customWidth="1"/>
-    <col min="6" max="6" width="53.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="45.7109375" customWidth="1"/>
+    <col min="6" max="6" width="53.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" customWidth="1"/>
-    <col min="19" max="19" width="13.88671875" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>59</v>
       </c>
@@ -2728,7 +2751,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
@@ -2783,7 +2806,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>60</v>
       </c>
@@ -2841,7 +2864,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>61</v>
       </c>
@@ -2898,7 +2921,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>64</v>
       </c>
@@ -2952,7 +2975,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E7" s="19" t="s">
         <v>4</v>
       </c>
@@ -3000,7 +3023,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>101</v>
       </c>
@@ -3055,7 +3078,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>102</v>
       </c>
@@ -3109,7 +3132,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
@@ -3164,7 +3187,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>114</v>
       </c>
@@ -3218,7 +3241,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E12" s="19" t="s">
         <v>9</v>
       </c>
@@ -3266,7 +3289,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="E13" s="19" t="s">
         <v>10</v>
@@ -3315,7 +3338,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="E14" s="19" t="s">
         <v>11</v>
@@ -3364,7 +3387,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E15" s="19" t="s">
         <v>12</v>
       </c>
@@ -3412,7 +3435,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
@@ -3460,7 +3483,7 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E17" s="19" t="s">
         <v>14</v>
       </c>
@@ -3508,7 +3531,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E18" s="19" t="s">
         <v>15</v>
       </c>
@@ -3556,7 +3579,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
@@ -3604,7 +3627,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
@@ -3650,7 +3673,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E21" s="19" t="s">
         <v>26</v>
       </c>
@@ -3698,7 +3721,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E22" s="19" t="s">
         <v>27</v>
       </c>
@@ -3746,7 +3769,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E23" s="19" t="s">
         <v>28</v>
       </c>
@@ -3794,7 +3817,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E24" s="19" t="s">
         <v>29</v>
       </c>
@@ -3842,7 +3865,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E25" s="19" t="s">
         <v>30</v>
       </c>
@@ -3888,7 +3911,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E26" s="19" t="s">
         <v>31</v>
       </c>
@@ -3936,7 +3959,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
@@ -3984,7 +4007,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E28" s="19" t="s">
         <v>33</v>
       </c>
@@ -4032,7 +4055,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E29" s="19" t="s">
         <v>34</v>
       </c>
@@ -4080,7 +4103,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E30" s="19" t="s">
         <v>35</v>
       </c>
@@ -4128,7 +4151,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E31" s="19" t="s">
         <v>36</v>
       </c>
@@ -4174,7 +4197,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E32" s="19" t="s">
         <v>37</v>
       </c>
@@ -4222,7 +4245,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E33" s="19" t="s">
         <v>38</v>
       </c>
@@ -4270,7 +4293,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="34" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
@@ -4316,7 +4339,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E35" s="19" t="s">
         <v>90</v>
       </c>
@@ -4362,7 +4385,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="36" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E36" s="19" t="s">
         <v>91</v>
       </c>
@@ -4408,7 +4431,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="37" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E37" s="19" t="s">
         <v>92</v>
       </c>
@@ -4454,7 +4477,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E38" s="19" t="s">
         <v>93</v>
       </c>
@@ -4500,7 +4523,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="39" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E39" s="31" t="s">
         <v>94</v>
       </c>
@@ -4546,7 +4569,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="40" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E40" s="32" t="s">
         <v>116</v>
       </c>
@@ -4592,7 +4615,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="41" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E41" s="39" t="s">
         <v>118</v>
       </c>
@@ -4638,7 +4661,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="42" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N42" s="6">
         <v>39</v>
       </c>
@@ -4662,7 +4685,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="43" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N43" s="6">
         <v>40</v>
       </c>
@@ -4686,7 +4709,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="44" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N44" s="6">
         <v>41</v>
       </c>
@@ -4710,7 +4733,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="45" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N45" s="6">
         <v>42</v>
       </c>
@@ -4734,7 +4757,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="46" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N46" s="6">
         <v>43</v>
       </c>
@@ -4758,7 +4781,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="47" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N47" s="6">
         <v>44</v>
       </c>
@@ -4782,7 +4805,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="48" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N48" s="6">
         <v>45</v>
       </c>
@@ -4806,7 +4829,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="49" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N49" s="6">
         <v>46</v>
       </c>
@@ -4830,7 +4853,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="50" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N50" s="6">
         <v>47</v>
       </c>
@@ -4854,7 +4877,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="51" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N51" s="6">
         <v>48</v>
       </c>
@@ -4878,7 +4901,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="52" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N52" s="6">
         <v>49</v>
       </c>
@@ -4902,7 +4925,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="53" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N53" s="6">
         <v>50</v>
       </c>
@@ -4926,7 +4949,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="54" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N54" s="6">
         <v>51</v>
       </c>
@@ -4950,7 +4973,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="55" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N55" s="6">
         <v>52</v>
       </c>
@@ -4974,7 +4997,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="56" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N56" s="6">
         <v>53</v>
       </c>
@@ -4998,7 +5021,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="57" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N57" s="6">
         <v>54</v>
       </c>
@@ -5022,7 +5045,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="58" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N58" s="6">
         <v>55</v>
       </c>
@@ -5046,7 +5069,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="59" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N59" s="6">
         <v>56</v>
       </c>
@@ -5058,7 +5081,9 @@
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="Q59" s="6"/>
+      <c r="Q59" s="6">
+        <v>0</v>
+      </c>
       <c r="R59" s="6">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -5068,7 +5093,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="60" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N60" s="6">
         <v>57</v>
       </c>
@@ -5080,7 +5105,9 @@
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
-      <c r="Q60" s="6"/>
+      <c r="Q60" s="6">
+        <v>0</v>
+      </c>
       <c r="R60" s="6">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -5090,7 +5117,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="61" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N61" s="6">
         <v>58</v>
       </c>
@@ -5102,7 +5129,9 @@
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="Q61" s="6"/>
+      <c r="Q61" s="6">
+        <v>0</v>
+      </c>
       <c r="R61" s="6">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -5112,7 +5141,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="62" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N62" s="6">
         <v>59</v>
       </c>
@@ -5124,7 +5153,9 @@
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="Q62" s="6"/>
+      <c r="Q62" s="6">
+        <v>0</v>
+      </c>
       <c r="R62" s="6">
         <f t="shared" si="3"/>
         <v>90</v>
@@ -5134,7 +5165,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="63" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N63" s="6">
         <v>60</v>
       </c>
@@ -5156,7 +5187,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="64" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N64" s="6">
         <v>61</v>
       </c>
@@ -5178,7 +5209,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="65" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N65" s="6">
         <v>62</v>
       </c>
@@ -5200,7 +5231,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="66" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N66" s="6">
         <v>63</v>
       </c>
@@ -5222,7 +5253,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="67" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N67" s="6">
         <v>64</v>
       </c>
@@ -5244,7 +5275,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="68" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N68" s="6">
         <v>65</v>
       </c>
@@ -5266,7 +5297,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="69" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N69" s="6">
         <v>66</v>
       </c>
@@ -5288,7 +5319,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="70" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N70" s="6">
         <v>67</v>
       </c>
@@ -5310,7 +5341,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="71" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N71" s="6">
         <v>68</v>
       </c>
@@ -5332,7 +5363,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="72" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N72" s="6">
         <v>69</v>
       </c>
@@ -5354,7 +5385,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="73" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N73" s="6">
         <v>70</v>
       </c>
@@ -5376,7 +5407,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="74" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N74" s="6">
         <v>71</v>
       </c>
@@ -5398,7 +5429,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="75" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N75" s="6">
         <v>72</v>
       </c>
@@ -5420,7 +5451,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="76" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N76" s="6">
         <v>73</v>
       </c>
@@ -5442,7 +5473,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="77" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N77" s="6">
         <v>74</v>
       </c>
@@ -5464,7 +5495,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="78" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N78" s="6">
         <v>75</v>
       </c>
@@ -5486,7 +5517,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="79" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N79" s="6">
         <v>76</v>
       </c>
@@ -5508,7 +5539,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="80" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N80" s="6">
         <v>77</v>
       </c>
@@ -5530,7 +5561,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="81" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N81" s="6">
         <v>78</v>
       </c>
@@ -5552,7 +5583,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="82" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N82" s="6">
         <v>79</v>
       </c>
@@ -5574,7 +5605,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="83" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N83" s="6">
         <v>80</v>
       </c>
@@ -5596,7 +5627,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="84" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N84" s="6">
         <v>81</v>
       </c>
@@ -5618,7 +5649,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="85" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N85" s="6">
         <v>82</v>
       </c>
@@ -5640,7 +5671,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="86" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N86" s="6">
         <v>83</v>
       </c>
@@ -5662,7 +5693,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="87" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N87" s="6">
         <v>84</v>
       </c>
@@ -5684,7 +5715,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="88" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N88" s="6">
         <v>85</v>
       </c>
@@ -5706,7 +5737,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="89" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N89" s="6">
         <v>86</v>
       </c>
@@ -5728,7 +5759,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="90" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N90" s="6">
         <v>87</v>
       </c>
@@ -5750,7 +5781,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="91" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N91" s="6">
         <v>88</v>
       </c>
@@ -5772,7 +5803,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="92" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N92" s="6">
         <v>89</v>
       </c>
@@ -5794,7 +5825,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="93" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N93" s="6">
         <v>90</v>
       </c>
@@ -5816,7 +5847,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="94" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N94" s="6">
         <v>91</v>
       </c>
@@ -5837,7 +5868,7 @@
         <v>46154</v>
       </c>
     </row>
-    <row r="95" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N95" s="6">
         <v>92</v>
       </c>
@@ -5858,7 +5889,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N96" s="6">
         <v>93</v>
       </c>
@@ -5879,7 +5910,7 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="97" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="97" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N97" s="6">
         <v>94</v>
       </c>
@@ -5900,7 +5931,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="98" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="98" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N98" s="6">
         <v>95</v>
       </c>
@@ -5921,7 +5952,7 @@
         <v>46158</v>
       </c>
     </row>
-    <row r="99" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="99" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N99" s="6">
         <v>96</v>
       </c>
@@ -5942,7 +5973,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="100" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="100" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N100" s="6">
         <v>97</v>
       </c>
@@ -5963,7 +5994,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="101" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N101" s="6">
         <v>98</v>
       </c>
@@ -5984,7 +6015,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="102" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N102" s="6">
         <v>99</v>
       </c>
@@ -6005,7 +6036,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="103" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N103" s="6">
         <v>100</v>
       </c>
@@ -6026,7 +6057,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="104" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N104" s="6">
         <v>101</v>
       </c>
@@ -6047,7 +6078,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="105" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="105" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N105" s="6">
         <v>102</v>
       </c>
@@ -6068,7 +6099,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="106" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N106" s="6">
         <v>103</v>
       </c>
@@ -6089,7 +6120,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="107" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N107" s="6">
         <v>104</v>
       </c>
@@ -6110,7 +6141,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="108" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N108" s="6">
         <v>105</v>
       </c>
@@ -6131,7 +6162,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="109" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N109" s="6">
         <v>106</v>
       </c>
@@ -6152,7 +6183,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="110" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N110" s="6">
         <v>107</v>
       </c>
@@ -6173,7 +6204,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="111" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="111" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N111" s="6">
         <v>108</v>
       </c>
@@ -6194,7 +6225,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="112" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="112" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N112" s="6">
         <v>109</v>
       </c>
@@ -6215,7 +6246,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="113" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N113" s="6">
         <v>110</v>
       </c>
@@ -6236,7 +6267,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="114" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N114" s="6">
         <v>111</v>
       </c>
@@ -6257,7 +6288,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="115" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N115" s="6">
         <v>112</v>
       </c>
@@ -6278,7 +6309,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="116" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N116" s="6">
         <v>113</v>
       </c>
@@ -6299,7 +6330,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="117" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N117" s="6">
         <v>114</v>
       </c>
@@ -6320,7 +6351,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="118" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="14:19" x14ac:dyDescent="0.25">
       <c r="S118" s="5"/>
     </row>
   </sheetData>
@@ -6383,4 +6414,948 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FF7EC3-657A-4070-AE9C-58B86EBA694A}">
+  <dimension ref="E5:O21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="55.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E6" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="23">
+        <v>3</v>
+      </c>
+      <c r="J6" s="21">
+        <v>3</v>
+      </c>
+      <c r="K6" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E7" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="25">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20">
+        <v>1</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E8" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="27">
+        <v>13</v>
+      </c>
+      <c r="J8" s="20">
+        <v>1</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="27">
+        <v>13</v>
+      </c>
+      <c r="J9" s="20">
+        <v>1</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="27">
+        <v>13</v>
+      </c>
+      <c r="J10" s="22">
+        <v>2</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="25">
+        <v>8</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="24">
+        <v>5</v>
+      </c>
+      <c r="J12" s="22">
+        <v>2</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E13" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="23">
+        <v>3</v>
+      </c>
+      <c r="J13" s="21">
+        <v>3</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="27">
+        <v>13</v>
+      </c>
+      <c r="J14" s="20">
+        <v>1</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="25">
+        <v>8</v>
+      </c>
+      <c r="J15" s="20">
+        <v>1</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E16" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="24">
+        <v>5</v>
+      </c>
+      <c r="J16" s="22">
+        <v>2</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="24">
+        <v>5</v>
+      </c>
+      <c r="J17" s="22">
+        <v>2</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E18" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="23">
+        <v>3</v>
+      </c>
+      <c r="J18" s="21">
+        <v>3</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="24">
+        <v>5</v>
+      </c>
+      <c r="J19" s="21">
+        <v>3</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E20" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="23">
+        <v>3</v>
+      </c>
+      <c r="J20" s="20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="24">
+        <v>5</v>
+      </c>
+      <c r="J21" s="20">
+        <v>1</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C898B-4D90-40D3-AB4B-229545D6799D}">
+  <dimension ref="E5:O20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="46.28515625" customWidth="1"/>
+    <col min="6" max="6" width="53.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E5" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="23">
+        <v>3</v>
+      </c>
+      <c r="J5" s="22">
+        <v>2</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E6" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="23">
+        <v>3</v>
+      </c>
+      <c r="J6" s="22">
+        <v>2</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="N6" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E7" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="25">
+        <v>8</v>
+      </c>
+      <c r="J7" s="21">
+        <v>3</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="O7" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E8" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="27">
+        <v>13</v>
+      </c>
+      <c r="J8" s="20">
+        <v>1</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="27">
+        <v>13</v>
+      </c>
+      <c r="J9" s="20">
+        <v>1</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E10" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="25">
+        <v>8</v>
+      </c>
+      <c r="J10" s="22">
+        <v>2</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="25">
+        <v>8</v>
+      </c>
+      <c r="J11" s="22">
+        <v>2</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="23">
+        <v>3</v>
+      </c>
+      <c r="J12" s="21">
+        <v>3</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E13" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="24">
+        <v>5</v>
+      </c>
+      <c r="J13" s="21">
+        <v>3</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E14" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="25">
+        <v>8</v>
+      </c>
+      <c r="J14" s="20">
+        <v>1</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E15" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="25">
+        <v>8</v>
+      </c>
+      <c r="J15" s="22">
+        <v>2</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="5:15" x14ac:dyDescent="0.25">
+      <c r="E16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="24">
+        <v>5</v>
+      </c>
+      <c r="J16" s="20">
+        <v>1</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="24">
+        <v>5</v>
+      </c>
+      <c r="J17" s="20">
+        <v>1</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="4"/>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="24">
+        <v>5</v>
+      </c>
+      <c r="J18" s="21">
+        <v>3</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="23">
+        <v>3</v>
+      </c>
+      <c r="J19" s="21">
+        <v>3</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="23">
+        <v>3</v>
+      </c>
+      <c r="J20" s="20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -5,17 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9158A729-86B7-43D7-98AC-F1DF5A4FB052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60A16035-DD5B-47F5-925C-A529310C7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog" sheetId="1" r:id="rId1"/>
-    <sheet name="Sprint01" sheetId="2" r:id="rId2"/>
-    <sheet name="Sprint02" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -455,7 +453,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,6 +544,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E6A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -624,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -739,12 +743,18 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFB5E6A2"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -862,7 +872,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Backlog!$P$3:$P$117</c:f>
+              <c:f>Planilha1!$P$3:$P$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="115"/>
@@ -1225,15 +1235,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Backlog!$R$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>272</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Pendente</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="34925" cap="rnd">
@@ -1255,10 +1257,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Backlog!$R$3:$R$62</c:f>
+              <c:f>Planilha1!$R$3:$R$64</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>272</c:v>
                 </c:pt>
@@ -1431,13 +1433,19 @@
                   <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>90</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>90</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>90</c:v>
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>79</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1537,7 +1545,6 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2321,14 +2328,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>420222</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44441</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>158002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>818030</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>14277</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2676,29 +2683,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
   <dimension ref="A2:T118"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" customWidth="1"/>
-    <col min="6" max="6" width="53.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="45.6640625" customWidth="1"/>
+    <col min="6" max="6" width="53.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="16" max="16" width="17.6640625" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" customWidth="1"/>
+    <col min="19" max="19" width="13.88671875" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>59</v>
       </c>
@@ -2751,7 +2758,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
@@ -2806,7 +2813,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>60</v>
       </c>
@@ -2864,7 +2871,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>61</v>
       </c>
@@ -2921,7 +2928,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>64</v>
       </c>
@@ -2975,7 +2982,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E7" s="19" t="s">
         <v>4</v>
       </c>
@@ -3023,7 +3030,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>101</v>
       </c>
@@ -3078,7 +3085,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>102</v>
       </c>
@@ -3132,7 +3139,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
@@ -3187,7 +3194,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>114</v>
       </c>
@@ -3241,7 +3248,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E12" s="19" t="s">
         <v>9</v>
       </c>
@@ -3289,7 +3296,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="E13" s="19" t="s">
         <v>10</v>
@@ -3338,7 +3345,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="E14" s="19" t="s">
         <v>11</v>
@@ -3387,7 +3394,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E15" s="19" t="s">
         <v>12</v>
       </c>
@@ -3435,7 +3442,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
@@ -3483,7 +3490,7 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E17" s="19" t="s">
         <v>14</v>
       </c>
@@ -3531,7 +3538,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E18" s="19" t="s">
         <v>15</v>
       </c>
@@ -3579,7 +3586,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
@@ -3627,7 +3634,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
@@ -3649,7 +3656,9 @@
       <c r="K20" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="L20" s="4"/>
+      <c r="L20" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="N20" s="6">
         <v>17</v>
       </c>
@@ -3673,7 +3682,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E21" s="19" t="s">
         <v>26</v>
       </c>
@@ -3721,7 +3730,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E22" s="19" t="s">
         <v>27</v>
       </c>
@@ -3769,7 +3778,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E23" s="19" t="s">
         <v>28</v>
       </c>
@@ -3817,7 +3826,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E24" s="19" t="s">
         <v>29</v>
       </c>
@@ -3865,11 +3874,11 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E25" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="44" t="s">
         <v>74</v>
       </c>
       <c r="G25" s="21" t="s">
@@ -3887,7 +3896,9 @@
       <c r="K25" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="L25" s="4"/>
+      <c r="L25" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="N25" s="6">
         <v>22</v>
       </c>
@@ -3911,11 +3922,11 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E26" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="44" t="s">
         <v>79</v>
       </c>
       <c r="G26" s="21" t="s">
@@ -3959,7 +3970,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
@@ -4007,7 +4018,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E28" s="19" t="s">
         <v>33</v>
       </c>
@@ -4055,7 +4066,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E29" s="19" t="s">
         <v>34</v>
       </c>
@@ -4103,7 +4114,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E30" s="19" t="s">
         <v>35</v>
       </c>
@@ -4151,7 +4162,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E31" s="19" t="s">
         <v>36</v>
       </c>
@@ -4173,7 +4184,9 @@
       <c r="K31" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="L31" s="4"/>
+      <c r="L31" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="N31" s="6">
         <v>28</v>
       </c>
@@ -4197,7 +4210,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E32" s="19" t="s">
         <v>37</v>
       </c>
@@ -4245,11 +4258,11 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E33" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="44" t="s">
         <v>86</v>
       </c>
       <c r="G33" s="21" t="s">
@@ -4293,7 +4306,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="34" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
@@ -4315,7 +4328,9 @@
       <c r="K34" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="L34" s="4"/>
+      <c r="L34" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="N34" s="6">
         <v>31</v>
       </c>
@@ -4339,7 +4354,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E35" s="19" t="s">
         <v>90</v>
       </c>
@@ -4385,7 +4400,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="36" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E36" s="19" t="s">
         <v>91</v>
       </c>
@@ -4431,7 +4446,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="37" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E37" s="19" t="s">
         <v>92</v>
       </c>
@@ -4477,7 +4492,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E38" s="19" t="s">
         <v>93</v>
       </c>
@@ -4523,7 +4538,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="39" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E39" s="31" t="s">
         <v>94</v>
       </c>
@@ -4569,7 +4584,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="40" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E40" s="32" t="s">
         <v>116</v>
       </c>
@@ -4615,7 +4630,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="41" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:19" x14ac:dyDescent="0.3">
       <c r="E41" s="39" t="s">
         <v>118</v>
       </c>
@@ -4661,7 +4676,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="42" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N42" s="6">
         <v>39</v>
       </c>
@@ -4685,7 +4700,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="43" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N43" s="6">
         <v>40</v>
       </c>
@@ -4709,7 +4724,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="44" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N44" s="6">
         <v>41</v>
       </c>
@@ -4733,7 +4748,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="45" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N45" s="6">
         <v>42</v>
       </c>
@@ -4757,7 +4772,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="46" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N46" s="6">
         <v>43</v>
       </c>
@@ -4781,7 +4796,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="47" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N47" s="6">
         <v>44</v>
       </c>
@@ -4805,7 +4820,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="48" spans="5:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:19" x14ac:dyDescent="0.3">
       <c r="N48" s="6">
         <v>45</v>
       </c>
@@ -4829,7 +4844,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N49" s="6">
         <v>46</v>
       </c>
@@ -4853,7 +4868,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N50" s="6">
         <v>47</v>
       </c>
@@ -4877,7 +4892,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="51" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N51" s="6">
         <v>48</v>
       </c>
@@ -4901,7 +4916,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="52" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N52" s="6">
         <v>49</v>
       </c>
@@ -4925,7 +4940,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="53" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N53" s="6">
         <v>50</v>
       </c>
@@ -4949,7 +4964,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="54" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N54" s="6">
         <v>51</v>
       </c>
@@ -4973,7 +4988,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="55" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N55" s="6">
         <v>52</v>
       </c>
@@ -4997,7 +5012,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="56" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N56" s="6">
         <v>53</v>
       </c>
@@ -5021,7 +5036,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="57" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N57" s="6">
         <v>54</v>
       </c>
@@ -5045,7 +5060,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="58" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N58" s="6">
         <v>55</v>
       </c>
@@ -5069,7 +5084,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="59" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N59" s="6">
         <v>56</v>
       </c>
@@ -5093,7 +5108,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="60" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N60" s="6">
         <v>57</v>
       </c>
@@ -5106,18 +5121,18 @@
         <v>101</v>
       </c>
       <c r="Q60" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S60" s="15">
         <f t="shared" si="2"/>
         <v>46120</v>
       </c>
     </row>
-    <row r="61" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N61" s="6">
         <v>58</v>
       </c>
@@ -5134,14 +5149,14 @@
       </c>
       <c r="R61" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S61" s="15">
         <f t="shared" si="2"/>
         <v>46121</v>
       </c>
     </row>
-    <row r="62" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N62" s="6">
         <v>59</v>
       </c>
@@ -5158,14 +5173,14 @@
       </c>
       <c r="R62" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S62" s="15">
         <f t="shared" si="2"/>
         <v>46122</v>
       </c>
     </row>
-    <row r="63" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N63" s="6">
         <v>60</v>
       </c>
@@ -5177,17 +5192,19 @@
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="Q63" s="6"/>
+      <c r="Q63" s="6">
+        <v>0</v>
+      </c>
       <c r="R63" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S63" s="15">
         <f t="shared" si="2"/>
         <v>46123</v>
       </c>
     </row>
-    <row r="64" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N64" s="6">
         <v>61</v>
       </c>
@@ -5199,17 +5216,19 @@
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="Q64" s="6"/>
+      <c r="Q64" s="6">
+        <v>8</v>
+      </c>
       <c r="R64" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S64" s="15">
         <f t="shared" si="2"/>
         <v>46124</v>
       </c>
     </row>
-    <row r="65" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N65" s="6">
         <v>62</v>
       </c>
@@ -5224,14 +5243,14 @@
       <c r="Q65" s="6"/>
       <c r="R65" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S65" s="15">
         <f t="shared" si="2"/>
         <v>46125</v>
       </c>
     </row>
-    <row r="66" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N66" s="6">
         <v>63</v>
       </c>
@@ -5246,14 +5265,14 @@
       <c r="Q66" s="6"/>
       <c r="R66" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S66" s="15">
         <f t="shared" si="2"/>
         <v>46126</v>
       </c>
     </row>
-    <row r="67" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N67" s="6">
         <v>64</v>
       </c>
@@ -5268,14 +5287,14 @@
       <c r="Q67" s="6"/>
       <c r="R67" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S67" s="15">
         <f t="shared" si="2"/>
         <v>46127</v>
       </c>
     </row>
-    <row r="68" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N68" s="6">
         <v>65</v>
       </c>
@@ -5290,14 +5309,14 @@
       <c r="Q68" s="6"/>
       <c r="R68" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S68" s="15">
         <f t="shared" si="2"/>
         <v>46128</v>
       </c>
     </row>
-    <row r="69" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N69" s="6">
         <v>66</v>
       </c>
@@ -5312,14 +5331,14 @@
       <c r="Q69" s="6"/>
       <c r="R69" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S69" s="15">
         <f t="shared" ref="S69:S117" si="7">S68+1</f>
         <v>46129</v>
       </c>
     </row>
-    <row r="70" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N70" s="6">
         <v>67</v>
       </c>
@@ -5334,14 +5353,14 @@
       <c r="Q70" s="6"/>
       <c r="R70" s="6">
         <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S70" s="15">
         <f t="shared" si="7"/>
         <v>46130</v>
       </c>
     </row>
-    <row r="71" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N71" s="6">
         <v>68</v>
       </c>
@@ -5356,14 +5375,14 @@
       <c r="Q71" s="6"/>
       <c r="R71" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S71" s="15">
         <f t="shared" si="7"/>
         <v>46131</v>
       </c>
     </row>
-    <row r="72" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N72" s="6">
         <v>69</v>
       </c>
@@ -5378,14 +5397,14 @@
       <c r="Q72" s="6"/>
       <c r="R72" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S72" s="15">
         <f t="shared" si="7"/>
         <v>46132</v>
       </c>
     </row>
-    <row r="73" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N73" s="6">
         <v>70</v>
       </c>
@@ -5400,14 +5419,14 @@
       <c r="Q73" s="6"/>
       <c r="R73" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S73" s="15">
         <f t="shared" si="7"/>
         <v>46133</v>
       </c>
     </row>
-    <row r="74" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N74" s="6">
         <v>71</v>
       </c>
@@ -5422,14 +5441,14 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S74" s="15">
         <f t="shared" si="7"/>
         <v>46134</v>
       </c>
     </row>
-    <row r="75" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N75" s="6">
         <v>72</v>
       </c>
@@ -5444,14 +5463,14 @@
       <c r="Q75" s="6"/>
       <c r="R75" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S75" s="16">
         <f t="shared" si="7"/>
         <v>46135</v>
       </c>
     </row>
-    <row r="76" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N76" s="6">
         <v>73</v>
       </c>
@@ -5466,14 +5485,14 @@
       <c r="Q76" s="6"/>
       <c r="R76" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S76" s="16">
         <f t="shared" si="7"/>
         <v>46136</v>
       </c>
     </row>
-    <row r="77" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N77" s="6">
         <v>74</v>
       </c>
@@ -5488,14 +5507,14 @@
       <c r="Q77" s="6"/>
       <c r="R77" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S77" s="16">
         <f t="shared" si="7"/>
         <v>46137</v>
       </c>
     </row>
-    <row r="78" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N78" s="6">
         <v>75</v>
       </c>
@@ -5510,14 +5529,14 @@
       <c r="Q78" s="6"/>
       <c r="R78" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S78" s="16">
         <f t="shared" si="7"/>
         <v>46138</v>
       </c>
     </row>
-    <row r="79" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N79" s="6">
         <v>76</v>
       </c>
@@ -5532,14 +5551,14 @@
       <c r="Q79" s="6"/>
       <c r="R79" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S79" s="16">
         <f t="shared" si="7"/>
         <v>46139</v>
       </c>
     </row>
-    <row r="80" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N80" s="6">
         <v>77</v>
       </c>
@@ -5554,14 +5573,14 @@
       <c r="Q80" s="6"/>
       <c r="R80" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S80" s="16">
         <f t="shared" si="7"/>
         <v>46140</v>
       </c>
     </row>
-    <row r="81" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N81" s="6">
         <v>78</v>
       </c>
@@ -5576,14 +5595,14 @@
       <c r="Q81" s="6"/>
       <c r="R81" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S81" s="16">
         <f t="shared" si="7"/>
         <v>46141</v>
       </c>
     </row>
-    <row r="82" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N82" s="6">
         <v>79</v>
       </c>
@@ -5598,14 +5617,14 @@
       <c r="Q82" s="6"/>
       <c r="R82" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S82" s="16">
         <f t="shared" si="7"/>
         <v>46142</v>
       </c>
     </row>
-    <row r="83" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N83" s="6">
         <v>80</v>
       </c>
@@ -5620,14 +5639,14 @@
       <c r="Q83" s="6"/>
       <c r="R83" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S83" s="16">
         <f t="shared" si="7"/>
         <v>46143</v>
       </c>
     </row>
-    <row r="84" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N84" s="6">
         <v>81</v>
       </c>
@@ -5642,14 +5661,14 @@
       <c r="Q84" s="6"/>
       <c r="R84" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S84" s="16">
         <f t="shared" si="7"/>
         <v>46144</v>
       </c>
     </row>
-    <row r="85" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N85" s="6">
         <v>82</v>
       </c>
@@ -5664,14 +5683,14 @@
       <c r="Q85" s="6"/>
       <c r="R85" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S85" s="16">
         <f t="shared" si="7"/>
         <v>46145</v>
       </c>
     </row>
-    <row r="86" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N86" s="6">
         <v>83</v>
       </c>
@@ -5686,14 +5705,14 @@
       <c r="Q86" s="6"/>
       <c r="R86" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S86" s="16">
         <f t="shared" si="7"/>
         <v>46146</v>
       </c>
     </row>
-    <row r="87" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N87" s="6">
         <v>84</v>
       </c>
@@ -5708,14 +5727,14 @@
       <c r="Q87" s="6"/>
       <c r="R87" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S87" s="16">
         <f t="shared" si="7"/>
         <v>46147</v>
       </c>
     </row>
-    <row r="88" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N88" s="6">
         <v>85</v>
       </c>
@@ -5730,14 +5749,14 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S88" s="16">
         <f t="shared" si="7"/>
         <v>46148</v>
       </c>
     </row>
-    <row r="89" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N89" s="6">
         <v>86</v>
       </c>
@@ -5752,14 +5771,14 @@
       <c r="Q89" s="6"/>
       <c r="R89" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S89" s="16">
         <f t="shared" si="7"/>
         <v>46149</v>
       </c>
     </row>
-    <row r="90" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="90" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N90" s="6">
         <v>87</v>
       </c>
@@ -5774,14 +5793,14 @@
       <c r="Q90" s="6"/>
       <c r="R90" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S90" s="16">
         <f t="shared" si="7"/>
         <v>46150</v>
       </c>
     </row>
-    <row r="91" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="91" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N91" s="6">
         <v>88</v>
       </c>
@@ -5796,14 +5815,14 @@
       <c r="Q91" s="6"/>
       <c r="R91" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S91" s="16">
         <f t="shared" si="7"/>
         <v>46151</v>
       </c>
     </row>
-    <row r="92" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="92" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N92" s="6">
         <v>89</v>
       </c>
@@ -5818,14 +5837,14 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S92" s="16">
         <f t="shared" si="7"/>
         <v>46152</v>
       </c>
     </row>
-    <row r="93" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="93" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N93" s="6">
         <v>90</v>
       </c>
@@ -5840,14 +5859,14 @@
       <c r="Q93" s="6"/>
       <c r="R93" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S93" s="16">
         <f t="shared" si="7"/>
         <v>46153</v>
       </c>
     </row>
-    <row r="94" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="94" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N94" s="6">
         <v>91</v>
       </c>
@@ -5861,14 +5880,14 @@
       <c r="Q94" s="6"/>
       <c r="R94" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S94" s="16">
         <f t="shared" si="7"/>
         <v>46154</v>
       </c>
     </row>
-    <row r="95" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="95" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N95" s="6">
         <v>92</v>
       </c>
@@ -5882,14 +5901,14 @@
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S95" s="16">
         <f t="shared" si="7"/>
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="96" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N96" s="6">
         <v>93</v>
       </c>
@@ -5903,14 +5922,14 @@
       <c r="Q96" s="6"/>
       <c r="R96" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S96" s="16">
         <f t="shared" si="7"/>
         <v>46156</v>
       </c>
     </row>
-    <row r="97" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="97" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N97" s="6">
         <v>94</v>
       </c>
@@ -5924,14 +5943,14 @@
       <c r="Q97" s="6"/>
       <c r="R97" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S97" s="16">
         <f t="shared" si="7"/>
         <v>46157</v>
       </c>
     </row>
-    <row r="98" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="98" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N98" s="6">
         <v>95</v>
       </c>
@@ -5945,14 +5964,14 @@
       <c r="Q98" s="6"/>
       <c r="R98" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S98" s="16">
         <f t="shared" si="7"/>
         <v>46158</v>
       </c>
     </row>
-    <row r="99" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N99" s="6">
         <v>96</v>
       </c>
@@ -5966,14 +5985,14 @@
       <c r="Q99" s="6"/>
       <c r="R99" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S99" s="16">
         <f t="shared" si="7"/>
         <v>46159</v>
       </c>
     </row>
-    <row r="100" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="100" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N100" s="6">
         <v>97</v>
       </c>
@@ -5987,14 +6006,14 @@
       <c r="Q100" s="6"/>
       <c r="R100" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S100" s="16">
         <f t="shared" si="7"/>
         <v>46160</v>
       </c>
     </row>
-    <row r="101" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="101" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N101" s="6">
         <v>98</v>
       </c>
@@ -6008,14 +6027,14 @@
       <c r="Q101" s="6"/>
       <c r="R101" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S101" s="16">
         <f t="shared" si="7"/>
         <v>46161</v>
       </c>
     </row>
-    <row r="102" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N102" s="6">
         <v>99</v>
       </c>
@@ -6029,14 +6048,14 @@
       <c r="Q102" s="6"/>
       <c r="R102" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S102" s="16">
         <f t="shared" si="7"/>
         <v>46162</v>
       </c>
     </row>
-    <row r="103" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N103" s="6">
         <v>100</v>
       </c>
@@ -6050,14 +6069,14 @@
       <c r="Q103" s="6"/>
       <c r="R103" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S103" s="16">
         <f t="shared" si="7"/>
         <v>46163</v>
       </c>
     </row>
-    <row r="104" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="104" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N104" s="6">
         <v>101</v>
       </c>
@@ -6071,14 +6090,14 @@
       <c r="Q104" s="6"/>
       <c r="R104" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S104" s="16">
         <f t="shared" si="7"/>
         <v>46164</v>
       </c>
     </row>
-    <row r="105" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N105" s="6">
         <v>102</v>
       </c>
@@ -6092,14 +6111,14 @@
       <c r="Q105" s="6"/>
       <c r="R105" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S105" s="16">
         <f t="shared" si="7"/>
         <v>46165</v>
       </c>
     </row>
-    <row r="106" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="106" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N106" s="6">
         <v>103</v>
       </c>
@@ -6113,14 +6132,14 @@
       <c r="Q106" s="6"/>
       <c r="R106" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S106" s="16">
         <f t="shared" si="7"/>
         <v>46166</v>
       </c>
     </row>
-    <row r="107" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="107" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N107" s="6">
         <v>104</v>
       </c>
@@ -6134,14 +6153,14 @@
       <c r="Q107" s="6"/>
       <c r="R107" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S107" s="16">
         <f t="shared" si="7"/>
         <v>46167</v>
       </c>
     </row>
-    <row r="108" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="108" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N108" s="6">
         <v>105</v>
       </c>
@@ -6155,14 +6174,14 @@
       <c r="Q108" s="6"/>
       <c r="R108" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S108" s="16">
         <f t="shared" si="7"/>
         <v>46168</v>
       </c>
     </row>
-    <row r="109" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N109" s="6">
         <v>106</v>
       </c>
@@ -6176,14 +6195,14 @@
       <c r="Q109" s="6"/>
       <c r="R109" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S109" s="16">
         <f t="shared" si="7"/>
         <v>46169</v>
       </c>
     </row>
-    <row r="110" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="110" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N110" s="6">
         <v>107</v>
       </c>
@@ -6197,14 +6216,14 @@
       <c r="Q110" s="6"/>
       <c r="R110" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S110" s="16">
         <f t="shared" si="7"/>
         <v>46170</v>
       </c>
     </row>
-    <row r="111" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="111" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N111" s="6">
         <v>108</v>
       </c>
@@ -6218,14 +6237,14 @@
       <c r="Q111" s="6"/>
       <c r="R111" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S111" s="16">
         <f t="shared" si="7"/>
         <v>46171</v>
       </c>
     </row>
-    <row r="112" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N112" s="6">
         <v>109</v>
       </c>
@@ -6239,14 +6258,14 @@
       <c r="Q112" s="6"/>
       <c r="R112" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S112" s="16">
         <f t="shared" si="7"/>
         <v>46172</v>
       </c>
     </row>
-    <row r="113" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N113" s="6">
         <v>110</v>
       </c>
@@ -6260,14 +6279,14 @@
       <c r="Q113" s="6"/>
       <c r="R113" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S113" s="16">
         <f t="shared" si="7"/>
         <v>46173</v>
       </c>
     </row>
-    <row r="114" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N114" s="6">
         <v>111</v>
       </c>
@@ -6281,14 +6300,14 @@
       <c r="Q114" s="6"/>
       <c r="R114" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S114" s="16">
         <f t="shared" si="7"/>
         <v>46174</v>
       </c>
     </row>
-    <row r="115" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N115" s="6">
         <v>112</v>
       </c>
@@ -6302,14 +6321,14 @@
       <c r="Q115" s="6"/>
       <c r="R115" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S115" s="16">
         <f t="shared" si="7"/>
         <v>46175</v>
       </c>
     </row>
-    <row r="116" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="116" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N116" s="6">
         <v>113</v>
       </c>
@@ -6323,14 +6342,14 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S116" s="16">
         <f t="shared" si="7"/>
         <v>46176</v>
       </c>
     </row>
-    <row r="117" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="117" spans="14:19" x14ac:dyDescent="0.3">
       <c r="N117" s="6">
         <v>114</v>
       </c>
@@ -6344,14 +6363,14 @@
       <c r="Q117" s="6"/>
       <c r="R117" s="6">
         <f t="shared" si="8"/>
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="S117" s="16">
         <f t="shared" si="7"/>
         <v>46177</v>
       </c>
     </row>
-    <row r="118" spans="14:19" x14ac:dyDescent="0.25">
+    <row r="118" spans="14:19" x14ac:dyDescent="0.3">
       <c r="S118" s="5"/>
     </row>
   </sheetData>
@@ -6414,948 +6433,4 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2FF7EC3-657A-4070-AE9C-58B86EBA694A}">
-  <dimension ref="E5:O21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="55.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="5:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E6" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="23">
-        <v>3</v>
-      </c>
-      <c r="J6" s="21">
-        <v>3</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E7" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="25">
-        <v>8</v>
-      </c>
-      <c r="J7" s="20">
-        <v>1</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="N7" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="O7" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E8" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="27">
-        <v>13</v>
-      </c>
-      <c r="J8" s="20">
-        <v>1</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E9" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="27">
-        <v>13</v>
-      </c>
-      <c r="J9" s="20">
-        <v>1</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="4">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E10" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="27">
-        <v>13</v>
-      </c>
-      <c r="J10" s="22">
-        <v>2</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E11" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="25">
-        <v>8</v>
-      </c>
-      <c r="J11" s="20">
-        <v>1</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="24">
-        <v>5</v>
-      </c>
-      <c r="J12" s="22">
-        <v>2</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="23">
-        <v>3</v>
-      </c>
-      <c r="J13" s="21">
-        <v>3</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E14" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="27">
-        <v>13</v>
-      </c>
-      <c r="J14" s="20">
-        <v>1</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E15" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="25">
-        <v>8</v>
-      </c>
-      <c r="J15" s="20">
-        <v>1</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E16" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="24">
-        <v>5</v>
-      </c>
-      <c r="J16" s="22">
-        <v>2</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="24">
-        <v>5</v>
-      </c>
-      <c r="J17" s="22">
-        <v>2</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E18" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I18" s="23">
-        <v>3</v>
-      </c>
-      <c r="J18" s="21">
-        <v>3</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="24">
-        <v>5</v>
-      </c>
-      <c r="J19" s="21">
-        <v>3</v>
-      </c>
-      <c r="K19" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E20" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="23">
-        <v>3</v>
-      </c>
-      <c r="J20" s="20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E21" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="24">
-        <v>5</v>
-      </c>
-      <c r="J21" s="20">
-        <v>1</v>
-      </c>
-      <c r="K21" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0C898B-4D90-40D3-AB4B-229545D6799D}">
-  <dimension ref="E5:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="46.28515625" customWidth="1"/>
-    <col min="6" max="6" width="53.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E5" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="23">
-        <v>3</v>
-      </c>
-      <c r="J5" s="22">
-        <v>2</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="O5" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E6" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="23">
-        <v>3</v>
-      </c>
-      <c r="J6" s="22">
-        <v>2</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="N6" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="25">
-        <v>8</v>
-      </c>
-      <c r="J7" s="21">
-        <v>3</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="O7" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E8" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="27">
-        <v>13</v>
-      </c>
-      <c r="J8" s="20">
-        <v>1</v>
-      </c>
-      <c r="K8" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E9" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="27">
-        <v>13</v>
-      </c>
-      <c r="J9" s="20">
-        <v>1</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" s="4">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E10" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H10" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="25">
-        <v>8</v>
-      </c>
-      <c r="J10" s="22">
-        <v>2</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E11" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="25">
-        <v>8</v>
-      </c>
-      <c r="J11" s="22">
-        <v>2</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E12" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="23">
-        <v>3</v>
-      </c>
-      <c r="J12" s="21">
-        <v>3</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E13" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="24">
-        <v>5</v>
-      </c>
-      <c r="J13" s="21">
-        <v>3</v>
-      </c>
-      <c r="K13" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E14" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="25">
-        <v>8</v>
-      </c>
-      <c r="J14" s="20">
-        <v>1</v>
-      </c>
-      <c r="K14" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E15" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="25">
-        <v>8</v>
-      </c>
-      <c r="J15" s="22">
-        <v>2</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E16" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="24">
-        <v>5</v>
-      </c>
-      <c r="J16" s="20">
-        <v>1</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E17" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="24">
-        <v>5</v>
-      </c>
-      <c r="J17" s="20">
-        <v>1</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E18" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="24">
-        <v>5</v>
-      </c>
-      <c r="J18" s="21">
-        <v>3</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E19" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I19" s="23">
-        <v>3</v>
-      </c>
-      <c r="J19" s="21">
-        <v>3</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E20" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="23">
-        <v>3</v>
-      </c>
-      <c r="J20" s="20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="L20" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albuq\Repositorios\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60A16035-DD5B-47F5-925C-A529310C7E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2550136C-158B-40BF-921F-D0CEC0D08F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -2683,29 +2683,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{552007D4-E79E-4A61-AC31-FF3BEBBC1490}">
   <dimension ref="A2:T118"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="5" max="5" width="45.6640625" customWidth="1"/>
-    <col min="6" max="6" width="53.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="45.7109375" customWidth="1"/>
+    <col min="6" max="6" width="53.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" customWidth="1"/>
     <col min="17" max="17" width="21" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" customWidth="1"/>
-    <col min="19" max="19" width="13.88671875" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>59</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>63</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>60</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>61</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>64</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E7" s="19" t="s">
         <v>4</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>101</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>102</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>103</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
         <v>114</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>46071</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E12" s="19" t="s">
         <v>9</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="E13" s="19" t="s">
         <v>10</v>
@@ -3345,7 +3345,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="E14" s="19" t="s">
         <v>11</v>
@@ -3394,7 +3394,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E15" s="19" t="s">
         <v>12</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E17" s="19" t="s">
         <v>14</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="18" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E18" s="19" t="s">
         <v>15</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="19" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E19" s="19" t="s">
         <v>24</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="20" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="21" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E21" s="19" t="s">
         <v>26</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="22" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E22" s="19" t="s">
         <v>27</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="23" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E23" s="19" t="s">
         <v>28</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="24" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E24" s="19" t="s">
         <v>29</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="25" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E25" s="19" t="s">
         <v>30</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="26" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E26" s="19" t="s">
         <v>31</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="27" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="28" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E28" s="19" t="s">
         <v>33</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="29" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E29" s="19" t="s">
         <v>34</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>46089</v>
       </c>
     </row>
-    <row r="30" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E30" s="19" t="s">
         <v>35</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="31" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E31" s="19" t="s">
         <v>36</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="32" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="32" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E32" s="19" t="s">
         <v>37</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="33" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E33" s="19" t="s">
         <v>38</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="34" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
@@ -4329,7 +4329,7 @@
         <v>88</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N34" s="6">
         <v>31</v>
@@ -4354,7 +4354,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="35" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E35" s="19" t="s">
         <v>90</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="36" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E36" s="19" t="s">
         <v>91</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>46096</v>
       </c>
     </row>
-    <row r="37" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E37" s="19" t="s">
         <v>92</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="38" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E38" s="19" t="s">
         <v>93</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="39" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E39" s="31" t="s">
         <v>94</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="40" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E40" s="32" t="s">
         <v>116</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="41" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E41" s="39" t="s">
         <v>118</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="42" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N42" s="6">
         <v>39</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>46102</v>
       </c>
     </row>
-    <row r="43" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="43" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N43" s="6">
         <v>40</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>46103</v>
       </c>
     </row>
-    <row r="44" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N44" s="6">
         <v>41</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="45" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N45" s="6">
         <v>42</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="46" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N46" s="6">
         <v>43</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="47" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N47" s="6">
         <v>44</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="48" spans="5:19" x14ac:dyDescent="0.3">
+    <row r="48" spans="5:19" x14ac:dyDescent="0.25">
       <c r="N48" s="6">
         <v>45</v>
       </c>
@@ -4844,7 +4844,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="49" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N49" s="6">
         <v>46</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="50" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N50" s="6">
         <v>47</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="51" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N51" s="6">
         <v>48</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="52" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N52" s="6">
         <v>49</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="53" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="53" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N53" s="6">
         <v>50</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="54" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N54" s="6">
         <v>51</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="55" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="55" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N55" s="6">
         <v>52</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="56" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N56" s="6">
         <v>53</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="57" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N57" s="6">
         <v>54</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="58" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N58" s="6">
         <v>55</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="59" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N59" s="6">
         <v>56</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="60" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N60" s="6">
         <v>57</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="61" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="61" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N61" s="6">
         <v>58</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="62" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N62" s="6">
         <v>59</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="63" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N63" s="6">
         <v>60</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>46123</v>
       </c>
     </row>
-    <row r="64" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N64" s="6">
         <v>61</v>
       </c>
@@ -5228,7 +5228,7 @@
         <v>46124</v>
       </c>
     </row>
-    <row r="65" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="65" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N65" s="6">
         <v>62</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="66" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N66" s="6">
         <v>63</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="67" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N67" s="6">
         <v>64</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="68" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N68" s="6">
         <v>65</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="69" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N69" s="6">
         <v>66</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="70" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N70" s="6">
         <v>67</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="71" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="71" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N71" s="6">
         <v>68</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="72" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="72" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N72" s="6">
         <v>69</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="73" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="73" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N73" s="6">
         <v>70</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="74" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="74" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N74" s="6">
         <v>71</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="75" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="75" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N75" s="6">
         <v>72</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="76" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="76" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N76" s="6">
         <v>73</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="77" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="77" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N77" s="6">
         <v>74</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="78" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="78" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N78" s="6">
         <v>75</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="79" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="79" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N79" s="6">
         <v>76</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="80" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="80" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N80" s="6">
         <v>77</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="81" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="81" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N81" s="6">
         <v>78</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="82" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="82" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N82" s="6">
         <v>79</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="83" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="83" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N83" s="6">
         <v>80</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="84" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="84" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N84" s="6">
         <v>81</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="85" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="85" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N85" s="6">
         <v>82</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="86" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="86" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N86" s="6">
         <v>83</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="87" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="87" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N87" s="6">
         <v>84</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="88" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="88" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N88" s="6">
         <v>85</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="89" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="89" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N89" s="6">
         <v>86</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="90" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="90" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N90" s="6">
         <v>87</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="91" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="91" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N91" s="6">
         <v>88</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="92" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="92" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N92" s="6">
         <v>89</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="93" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="93" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N93" s="6">
         <v>90</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="94" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="94" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N94" s="6">
         <v>91</v>
       </c>
@@ -5887,7 +5887,7 @@
         <v>46154</v>
       </c>
     </row>
-    <row r="95" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="95" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N95" s="6">
         <v>92</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="96" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N96" s="6">
         <v>93</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>46156</v>
       </c>
     </row>
-    <row r="97" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="97" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N97" s="6">
         <v>94</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="98" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="98" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N98" s="6">
         <v>95</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>46158</v>
       </c>
     </row>
-    <row r="99" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="99" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N99" s="6">
         <v>96</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>46159</v>
       </c>
     </row>
-    <row r="100" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="100" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N100" s="6">
         <v>97</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="101" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="101" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N101" s="6">
         <v>98</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="102" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="102" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N102" s="6">
         <v>99</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="103" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="103" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N103" s="6">
         <v>100</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="104" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="104" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N104" s="6">
         <v>101</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="105" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="105" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N105" s="6">
         <v>102</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="106" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="106" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N106" s="6">
         <v>103</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="107" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="107" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N107" s="6">
         <v>104</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="108" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="108" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N108" s="6">
         <v>105</v>
       </c>
@@ -6181,7 +6181,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="109" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="109" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N109" s="6">
         <v>106</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="110" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="110" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N110" s="6">
         <v>107</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="111" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="111" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N111" s="6">
         <v>108</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="112" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="112" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N112" s="6">
         <v>109</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="113" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N113" s="6">
         <v>110</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="114" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N114" s="6">
         <v>111</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="115" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N115" s="6">
         <v>112</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="116" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N116" s="6">
         <v>113</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="117" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="14:19" x14ac:dyDescent="0.25">
       <c r="N117" s="6">
         <v>114</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="118" spans="14:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="14:19" x14ac:dyDescent="0.25">
       <c r="S118" s="5"/>
     </row>
   </sheetData>

--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\albuq\Repositorios\ThermoChain\Documentações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2550136C-158B-40BF-921F-D0CEC0D08F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E1BC0-F719-4C17-85B8-61047038CE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
@@ -1257,10 +1257,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$R$3:$R$64</c:f>
+              <c:f>Planilha1!$R$3:$R$75</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="73"/>
                 <c:pt idx="0">
                   <c:v>272</c:v>
                 </c:pt>
@@ -1446,6 +1446,39 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>79</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4310,7 +4343,7 @@
       <c r="E34" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="44" t="s">
         <v>87</v>
       </c>
       <c r="G34" s="20" t="s">
@@ -5240,7 +5273,9 @@
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="Q65" s="6"/>
+      <c r="Q65" s="6">
+        <v>0</v>
+      </c>
       <c r="R65" s="6">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -5262,7 +5297,9 @@
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="Q66" s="6"/>
+      <c r="Q66" s="6">
+        <v>0</v>
+      </c>
       <c r="R66" s="6">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -5284,7 +5321,9 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="Q67" s="6"/>
+      <c r="Q67" s="6">
+        <v>0</v>
+      </c>
       <c r="R67" s="6">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -5306,7 +5345,9 @@
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="Q68" s="6"/>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
       <c r="R68" s="6">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -5328,7 +5369,9 @@
         <f t="shared" ref="P69:P93" si="6">P68-$O$4</f>
         <v>74</v>
       </c>
-      <c r="Q69" s="6"/>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
       <c r="R69" s="6">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -5350,7 +5393,9 @@
         <f t="shared" si="6"/>
         <v>71</v>
       </c>
-      <c r="Q70" s="6"/>
+      <c r="Q70" s="6">
+        <v>0</v>
+      </c>
       <c r="R70" s="6">
         <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
         <v>79</v>
@@ -5372,7 +5417,9 @@
         <f t="shared" si="6"/>
         <v>68</v>
       </c>
-      <c r="Q71" s="6"/>
+      <c r="Q71" s="6">
+        <v>0</v>
+      </c>
       <c r="R71" s="6">
         <f t="shared" si="8"/>
         <v>79</v>
@@ -5394,7 +5441,9 @@
         <f t="shared" si="6"/>
         <v>65</v>
       </c>
-      <c r="Q72" s="6"/>
+      <c r="Q72" s="6">
+        <v>0</v>
+      </c>
       <c r="R72" s="6">
         <f t="shared" si="8"/>
         <v>79</v>
@@ -5416,7 +5465,9 @@
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
-      <c r="Q73" s="6"/>
+      <c r="Q73" s="6">
+        <v>0</v>
+      </c>
       <c r="R73" s="6">
         <f t="shared" si="8"/>
         <v>79</v>
@@ -5438,10 +5489,12 @@
         <f t="shared" si="6"/>
         <v>59</v>
       </c>
-      <c r="Q74" s="6"/>
+      <c r="Q74" s="6">
+        <v>3</v>
+      </c>
       <c r="R74" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S74" s="15">
         <f t="shared" si="7"/>
@@ -5460,12 +5513,14 @@
         <f t="shared" si="6"/>
         <v>56</v>
       </c>
-      <c r="Q75" s="6"/>
+      <c r="Q75" s="6">
+        <v>0</v>
+      </c>
       <c r="R75" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S75" s="16">
+        <v>76</v>
+      </c>
+      <c r="S75" s="15">
         <f t="shared" si="7"/>
         <v>46135</v>
       </c>
@@ -5485,9 +5540,9 @@
       <c r="Q76" s="6"/>
       <c r="R76" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S76" s="16">
+        <v>76</v>
+      </c>
+      <c r="S76" s="15">
         <f t="shared" si="7"/>
         <v>46136</v>
       </c>
@@ -5507,9 +5562,9 @@
       <c r="Q77" s="6"/>
       <c r="R77" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S77" s="16">
+        <v>76</v>
+      </c>
+      <c r="S77" s="15">
         <f t="shared" si="7"/>
         <v>46137</v>
       </c>
@@ -5529,9 +5584,9 @@
       <c r="Q78" s="6"/>
       <c r="R78" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S78" s="16">
+        <v>76</v>
+      </c>
+      <c r="S78" s="15">
         <f t="shared" si="7"/>
         <v>46138</v>
       </c>
@@ -5551,9 +5606,9 @@
       <c r="Q79" s="6"/>
       <c r="R79" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S79" s="16">
+        <v>76</v>
+      </c>
+      <c r="S79" s="15">
         <f t="shared" si="7"/>
         <v>46139</v>
       </c>
@@ -5573,9 +5628,9 @@
       <c r="Q80" s="6"/>
       <c r="R80" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S80" s="16">
+        <v>76</v>
+      </c>
+      <c r="S80" s="15">
         <f t="shared" si="7"/>
         <v>46140</v>
       </c>
@@ -5595,9 +5650,9 @@
       <c r="Q81" s="6"/>
       <c r="R81" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S81" s="16">
+        <v>76</v>
+      </c>
+      <c r="S81" s="15">
         <f t="shared" si="7"/>
         <v>46141</v>
       </c>
@@ -5617,9 +5672,9 @@
       <c r="Q82" s="6"/>
       <c r="R82" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S82" s="16">
+        <v>76</v>
+      </c>
+      <c r="S82" s="15">
         <f t="shared" si="7"/>
         <v>46142</v>
       </c>
@@ -5639,9 +5694,9 @@
       <c r="Q83" s="6"/>
       <c r="R83" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S83" s="16">
+        <v>76</v>
+      </c>
+      <c r="S83" s="15">
         <f t="shared" si="7"/>
         <v>46143</v>
       </c>
@@ -5661,9 +5716,9 @@
       <c r="Q84" s="6"/>
       <c r="R84" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S84" s="16">
+        <v>76</v>
+      </c>
+      <c r="S84" s="15">
         <f t="shared" si="7"/>
         <v>46144</v>
       </c>
@@ -5683,9 +5738,9 @@
       <c r="Q85" s="6"/>
       <c r="R85" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S85" s="16">
+        <v>76</v>
+      </c>
+      <c r="S85" s="15">
         <f t="shared" si="7"/>
         <v>46145</v>
       </c>
@@ -5705,9 +5760,9 @@
       <c r="Q86" s="6"/>
       <c r="R86" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S86" s="16">
+        <v>76</v>
+      </c>
+      <c r="S86" s="15">
         <f t="shared" si="7"/>
         <v>46146</v>
       </c>
@@ -5727,9 +5782,9 @@
       <c r="Q87" s="6"/>
       <c r="R87" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="S87" s="16">
+        <v>76</v>
+      </c>
+      <c r="S87" s="15">
         <f t="shared" si="7"/>
         <v>46147</v>
       </c>
@@ -5749,7 +5804,7 @@
       <c r="Q88" s="6"/>
       <c r="R88" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S88" s="16">
         <f t="shared" si="7"/>
@@ -5771,7 +5826,7 @@
       <c r="Q89" s="6"/>
       <c r="R89" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S89" s="16">
         <f t="shared" si="7"/>
@@ -5793,7 +5848,7 @@
       <c r="Q90" s="6"/>
       <c r="R90" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S90" s="16">
         <f t="shared" si="7"/>
@@ -5815,7 +5870,7 @@
       <c r="Q91" s="6"/>
       <c r="R91" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S91" s="16">
         <f t="shared" si="7"/>
@@ -5837,7 +5892,7 @@
       <c r="Q92" s="6"/>
       <c r="R92" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S92" s="16">
         <f t="shared" si="7"/>
@@ -5859,7 +5914,7 @@
       <c r="Q93" s="6"/>
       <c r="R93" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S93" s="16">
         <f t="shared" si="7"/>
@@ -5880,7 +5935,7 @@
       <c r="Q94" s="6"/>
       <c r="R94" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S94" s="16">
         <f t="shared" si="7"/>
@@ -5901,7 +5956,7 @@
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S95" s="16">
         <f t="shared" si="7"/>
@@ -5922,7 +5977,7 @@
       <c r="Q96" s="6"/>
       <c r="R96" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S96" s="16">
         <f t="shared" si="7"/>
@@ -5943,7 +5998,7 @@
       <c r="Q97" s="6"/>
       <c r="R97" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S97" s="16">
         <f t="shared" si="7"/>
@@ -5964,7 +6019,7 @@
       <c r="Q98" s="6"/>
       <c r="R98" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S98" s="16">
         <f t="shared" si="7"/>
@@ -5985,7 +6040,7 @@
       <c r="Q99" s="6"/>
       <c r="R99" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S99" s="16">
         <f t="shared" si="7"/>
@@ -6006,7 +6061,7 @@
       <c r="Q100" s="6"/>
       <c r="R100" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S100" s="16">
         <f t="shared" si="7"/>
@@ -6027,7 +6082,7 @@
       <c r="Q101" s="6"/>
       <c r="R101" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S101" s="16">
         <f t="shared" si="7"/>
@@ -6048,7 +6103,7 @@
       <c r="Q102" s="6"/>
       <c r="R102" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S102" s="16">
         <f t="shared" si="7"/>
@@ -6069,7 +6124,7 @@
       <c r="Q103" s="6"/>
       <c r="R103" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S103" s="16">
         <f t="shared" si="7"/>
@@ -6090,7 +6145,7 @@
       <c r="Q104" s="6"/>
       <c r="R104" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S104" s="16">
         <f t="shared" si="7"/>
@@ -6111,7 +6166,7 @@
       <c r="Q105" s="6"/>
       <c r="R105" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S105" s="16">
         <f t="shared" si="7"/>
@@ -6132,7 +6187,7 @@
       <c r="Q106" s="6"/>
       <c r="R106" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S106" s="16">
         <f t="shared" si="7"/>
@@ -6153,7 +6208,7 @@
       <c r="Q107" s="6"/>
       <c r="R107" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S107" s="16">
         <f t="shared" si="7"/>
@@ -6174,7 +6229,7 @@
       <c r="Q108" s="6"/>
       <c r="R108" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S108" s="16">
         <f t="shared" si="7"/>
@@ -6195,7 +6250,7 @@
       <c r="Q109" s="6"/>
       <c r="R109" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S109" s="16">
         <f t="shared" si="7"/>
@@ -6216,7 +6271,7 @@
       <c r="Q110" s="6"/>
       <c r="R110" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S110" s="16">
         <f t="shared" si="7"/>
@@ -6237,7 +6292,7 @@
       <c r="Q111" s="6"/>
       <c r="R111" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S111" s="16">
         <f t="shared" si="7"/>
@@ -6258,7 +6313,7 @@
       <c r="Q112" s="6"/>
       <c r="R112" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S112" s="16">
         <f t="shared" si="7"/>
@@ -6279,7 +6334,7 @@
       <c r="Q113" s="6"/>
       <c r="R113" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S113" s="16">
         <f t="shared" si="7"/>
@@ -6300,7 +6355,7 @@
       <c r="Q114" s="6"/>
       <c r="R114" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S114" s="16">
         <f t="shared" si="7"/>
@@ -6321,7 +6376,7 @@
       <c r="Q115" s="6"/>
       <c r="R115" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S115" s="16">
         <f t="shared" si="7"/>
@@ -6342,7 +6397,7 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S116" s="16">
         <f t="shared" si="7"/>
@@ -6363,7 +6418,7 @@
       <c r="Q117" s="6"/>
       <c r="R117" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S117" s="16">
         <f t="shared" si="7"/>

--- a/Documentações/Backlog.xlsx
+++ b/Documentações/Backlog.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\OneDrive\Área de Trabalho\ThermoChain\Documentações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E1BC0-F719-4C17-85B8-61047038CE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100961CA-25F7-4948-986A-D9F783406DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88668B19-0EBA-47FC-AF05-5256D7A9BC46}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="BackLog" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint01" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint02" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="120">
   <si>
     <t>Projeto no github</t>
   </si>
@@ -453,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,12 +501,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -678,50 +674,49 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -731,19 +726,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,282 +867,282 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$P$3:$P$117</c:f>
+              <c:f>BackLog!$P$3:$P$117</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="115"/>
                 <c:pt idx="0">
-                  <c:v>272</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>269</c:v>
+                  <c:v>303</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>266</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>263</c:v>
+                  <c:v>297</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>260</c:v>
+                  <c:v>294</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>257</c:v>
+                  <c:v>291</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>254</c:v>
+                  <c:v>288</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>251</c:v>
+                  <c:v>285</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>248</c:v>
+                  <c:v>282</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>245</c:v>
+                  <c:v>279</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>242</c:v>
+                  <c:v>276</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>239</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>236</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>233</c:v>
+                  <c:v>267</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>230</c:v>
+                  <c:v>264</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>227</c:v>
+                  <c:v>261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>224</c:v>
+                  <c:v>258</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>221</c:v>
+                  <c:v>255</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>218</c:v>
+                  <c:v>252</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>215</c:v>
+                  <c:v>249</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>212</c:v>
+                  <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>209</c:v>
+                  <c:v>243</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>206</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>203</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>200</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>197</c:v>
+                  <c:v>231</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>194</c:v>
+                  <c:v>228</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>191</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>188</c:v>
+                  <c:v>222</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>185</c:v>
+                  <c:v>219</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>182</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>179</c:v>
+                  <c:v>213</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>176</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>173</c:v>
+                  <c:v>207</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>170</c:v>
+                  <c:v>204</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>167</c:v>
+                  <c:v>201</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>164</c:v>
+                  <c:v>198</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>161</c:v>
+                  <c:v>195</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>158</c:v>
+                  <c:v>192</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>155</c:v>
+                  <c:v>189</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>152</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>149</c:v>
+                  <c:v>183</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>146</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>143</c:v>
+                  <c:v>177</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>140</c:v>
+                  <c:v>174</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>137</c:v>
+                  <c:v>171</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>134</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>131</c:v>
+                  <c:v>165</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>128</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>125</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>122</c:v>
+                  <c:v>156</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>119</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>116</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>113</c:v>
+                  <c:v>147</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>110</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>107</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>104</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>101</c:v>
+                  <c:v>135</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>98</c:v>
+                  <c:v>132</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>95</c:v>
+                  <c:v>129</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>92</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>89</c:v>
+                  <c:v>123</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>86</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>83</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>80</c:v>
+                  <c:v>114</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>77</c:v>
+                  <c:v>111</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>74</c:v>
+                  <c:v>108</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>71</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>68</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>65</c:v>
+                  <c:v>99</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>62</c:v>
+                  <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>59</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>56</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>53</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>50</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>47</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>44</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>41</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>38</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>35</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>32</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>29</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>26</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>23</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>20</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>17</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>14</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>11</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>8</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>5</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="91">
                   <c:v>0</c:v>
@@ -1257,228 +1252,264 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!$R$3:$R$75</c:f>
+              <c:f>BackLog!$R$3:$R$87</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="73"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
-                  <c:v>272</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>272</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>272</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>270</c:v>
+                  <c:v>304</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>270</c:v>
+                  <c:v>304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>267</c:v>
+                  <c:v>301</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>266</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>262</c:v>
+                  <c:v>296</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>262</c:v>
+                  <c:v>296</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>257</c:v>
+                  <c:v>291</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>255</c:v>
+                  <c:v>289</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>249</c:v>
+                  <c:v>283</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>249</c:v>
+                  <c:v>283</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>273</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>242</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>239</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>231</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>231</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>222</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>218</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>208</c:v>
-                </c:pt>
                 <c:pt idx="20">
-                  <c:v>208</c:v>
+                  <c:v>242</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>200</c:v>
+                  <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="22">
+                  <c:v>228</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>207</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>201</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>194</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="31">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>193</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>185</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="36">
                   <c:v>185</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>178</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>173</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>167</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>167</c:v>
-                </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="37">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>179</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>163</c:v>
                 </c:pt>
-                <c:pt idx="30">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>151</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>151</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="41">
+                  <c:v>163</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>145</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="44">
                   <c:v>145</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="45">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>137</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>129</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>129</c:v>
-                </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="52">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>121</c:v>
                 </c:pt>
-                <c:pt idx="43">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>111</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>103</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>87</c:v>
-                </c:pt>
                 <c:pt idx="58">
-                  <c:v>87</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>87</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>87</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>79</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>76</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>76</c:v>
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2739,7 +2770,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>59</v>
       </c>
       <c r="B2" s="4">
@@ -2792,31 +2823,31 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>63</v>
       </c>
       <c r="B3" s="4">
         <v>5</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="23">
-        <v>3</v>
-      </c>
-      <c r="J3" s="21">
-        <v>3</v>
-      </c>
-      <c r="K3" s="24" t="s">
+      <c r="I3" s="22">
+        <v>3</v>
+      </c>
+      <c r="J3" s="20">
+        <v>3</v>
+      </c>
+      <c r="K3" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
@@ -2825,19 +2856,19 @@
       <c r="N3" s="6">
         <v>0</v>
       </c>
-      <c r="O3" s="29">
+      <c r="O3" s="28">
         <v>0</v>
       </c>
       <c r="P3" s="6">
         <f>B8</f>
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
       </c>
       <c r="R3" s="6">
         <f>B8</f>
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="S3" s="14">
         <v>46063</v>
@@ -2847,31 +2878,31 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>60</v>
       </c>
       <c r="B4" s="4">
         <v>8</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="24">
         <v>8</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <v>1</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L4" s="4" t="s">
@@ -2881,20 +2912,20 @@
         <f t="array" ref="N4:N117">_xlfn.SEQUENCE(114)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="28">
         <f t="shared" ref="O4:O35" si="0">$B$10</f>
         <v>3</v>
       </c>
       <c r="P4" s="6">
         <f>P3-$O$4</f>
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
       </c>
       <c r="R4" s="6">
         <f>R3-Q4</f>
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="S4" s="14">
         <f>S3+1</f>
@@ -2905,31 +2936,31 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>61</v>
       </c>
       <c r="B5" s="4">
         <v>13</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="H5" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="26">
         <v>13</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="19">
         <v>1</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -2938,20 +2969,20 @@
       <c r="N5" s="6">
         <v>2</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P5" s="6">
         <f t="shared" ref="P5:P68" si="1">P4-$O$4</f>
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
       </c>
       <c r="R5" s="6">
         <f>IF(Q5&lt;&gt;"",R4-Q5,R4)</f>
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="S5" s="14">
         <f t="shared" ref="S5:S68" si="2">S4+1</f>
@@ -2962,31 +2993,31 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="4">
         <v>21</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="26">
         <v>13</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="19">
         <v>1</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L6" s="4" t="s">
@@ -2995,20 +3026,20 @@
       <c r="N6" s="6">
         <v>3</v>
       </c>
-      <c r="O6" s="29">
+      <c r="O6" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P6" s="6">
         <f t="shared" si="1"/>
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="Q6" s="6">
         <v>2</v>
       </c>
       <c r="R6" s="6">
         <f t="shared" ref="R6:R69" si="3">IF(Q6&lt;&gt;"",R5-Q6,R5)</f>
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="S6" s="14">
         <f t="shared" si="2"/>
@@ -3016,25 +3047,25 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="26">
         <v>13</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="21">
         <v>2</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L7" s="4" t="s">
@@ -3043,20 +3074,20 @@
       <c r="N7" s="6">
         <v>4</v>
       </c>
-      <c r="O7" s="29">
+      <c r="O7" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P7" s="6">
         <f t="shared" si="1"/>
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
       </c>
       <c r="R7" s="6">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="S7" s="14">
         <f t="shared" si="2"/>
@@ -3068,28 +3099,28 @@
         <v>101</v>
       </c>
       <c r="B8" s="6">
-        <f>SUM(I3:I39)</f>
-        <v>272</v>
-      </c>
-      <c r="E8" s="19" t="s">
+        <f>SUM(I3:I41)</f>
+        <v>306</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>5</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <v>8</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="19">
         <v>1</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L8" s="4" t="s">
@@ -3098,20 +3129,20 @@
       <c r="N8" s="6">
         <v>5</v>
       </c>
-      <c r="O8" s="29">
+      <c r="O8" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P8" s="6">
         <f t="shared" si="1"/>
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="Q8" s="6">
         <v>3</v>
       </c>
       <c r="R8" s="6">
         <f t="shared" si="3"/>
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="S8" s="14">
         <f t="shared" si="2"/>
@@ -3125,25 +3156,25 @@
       <c r="B9" s="6">
         <v>114</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="23">
         <v>5</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="21">
         <v>2</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L9" s="4" t="s">
@@ -3152,20 +3183,20 @@
       <c r="N9" s="6">
         <v>6</v>
       </c>
-      <c r="O9" s="29">
+      <c r="O9" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P9" s="6">
         <f t="shared" si="1"/>
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="Q9" s="6">
         <v>1</v>
       </c>
       <c r="R9" s="6">
         <f t="shared" si="3"/>
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="S9" s="14">
         <f t="shared" si="2"/>
@@ -3180,25 +3211,25 @@
         <f>ROUNDUP(B8/B9, 0)</f>
         <v>3</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>7</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="23">
-        <v>3</v>
-      </c>
-      <c r="J10" s="21">
-        <v>3</v>
-      </c>
-      <c r="K10" s="24" t="s">
+      <c r="I10" s="22">
+        <v>3</v>
+      </c>
+      <c r="J10" s="20">
+        <v>3</v>
+      </c>
+      <c r="K10" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -3207,20 +3238,20 @@
       <c r="N10" s="6">
         <v>7</v>
       </c>
-      <c r="O10" s="29">
+      <c r="O10" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="1"/>
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="Q10" s="6">
         <v>4</v>
       </c>
       <c r="R10" s="6">
         <f t="shared" si="3"/>
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="S10" s="14">
         <f t="shared" si="2"/>
@@ -3228,31 +3259,31 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="29" t="s">
         <v>114</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="27" t="s">
+      <c r="H11" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="26">
         <v>13</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="19">
         <v>1</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -3261,20 +3292,20 @@
       <c r="N11" s="6">
         <v>8</v>
       </c>
-      <c r="O11" s="29">
+      <c r="O11" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P11" s="6">
         <f t="shared" si="1"/>
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
       </c>
       <c r="R11" s="6">
         <f t="shared" si="3"/>
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="S11" s="14">
         <f t="shared" si="2"/>
@@ -3282,25 +3313,25 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="18" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <v>8</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="19">
         <v>1</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -3309,20 +3340,20 @@
       <c r="N12" s="6">
         <v>9</v>
       </c>
-      <c r="O12" s="29">
+      <c r="O12" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P12" s="6">
         <f t="shared" si="1"/>
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="Q12" s="6">
         <v>5</v>
       </c>
       <c r="R12" s="6">
         <f t="shared" si="3"/>
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="S12" s="14">
         <f t="shared" si="2"/>
@@ -3331,25 +3362,25 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="18" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="23">
         <v>5</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="21">
         <v>2</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -3358,20 +3389,20 @@
       <c r="N13" s="6">
         <v>10</v>
       </c>
-      <c r="O13" s="29">
+      <c r="O13" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P13" s="6">
         <f t="shared" si="1"/>
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="Q13" s="6">
         <v>2</v>
       </c>
       <c r="R13" s="6">
         <f t="shared" si="3"/>
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="S13" s="14">
         <f t="shared" si="2"/>
@@ -3380,25 +3411,25 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="24" t="s">
+      <c r="H14" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="23">
         <v>5</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="21">
         <v>2</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L14" s="4" t="s">
@@ -3407,20 +3438,20 @@
       <c r="N14" s="6">
         <v>11</v>
       </c>
-      <c r="O14" s="29">
+      <c r="O14" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P14" s="6">
         <f t="shared" si="1"/>
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="Q14" s="6">
         <v>6</v>
       </c>
       <c r="R14" s="6">
         <f t="shared" si="3"/>
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="S14" s="14">
         <f t="shared" si="2"/>
@@ -3428,25 +3459,25 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="23">
-        <v>3</v>
-      </c>
-      <c r="J15" s="21">
-        <v>3</v>
-      </c>
-      <c r="K15" s="24" t="s">
+      <c r="I15" s="22">
+        <v>3</v>
+      </c>
+      <c r="J15" s="20">
+        <v>3</v>
+      </c>
+      <c r="K15" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -3455,20 +3486,20 @@
       <c r="N15" s="6">
         <v>12</v>
       </c>
-      <c r="O15" s="29">
+      <c r="O15" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P15" s="6">
         <f t="shared" si="1"/>
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
       </c>
       <c r="R15" s="6">
         <f t="shared" si="3"/>
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="S15" s="14">
         <f t="shared" si="2"/>
@@ -3476,25 +3507,25 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="23">
         <v>5</v>
       </c>
-      <c r="J16" s="21">
-        <v>3</v>
-      </c>
-      <c r="K16" s="24" t="s">
+      <c r="J16" s="20">
+        <v>3</v>
+      </c>
+      <c r="K16" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L16" s="4" t="s">
@@ -3503,20 +3534,20 @@
       <c r="N16" s="6">
         <v>13</v>
       </c>
-      <c r="O16" s="29">
+      <c r="O16" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P16" s="6">
         <f t="shared" si="1"/>
-        <v>233</v>
+        <v>267</v>
       </c>
       <c r="Q16" s="6">
         <v>7</v>
       </c>
       <c r="R16" s="6">
         <f t="shared" si="3"/>
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="S16" s="14">
         <f t="shared" si="2"/>
@@ -3524,25 +3555,25 @@
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I17" s="23">
-        <v>3</v>
-      </c>
-      <c r="J17" s="20">
+      <c r="I17" s="22">
+        <v>3</v>
+      </c>
+      <c r="J17" s="19">
         <v>1</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L17" s="4" t="s">
@@ -3551,20 +3582,20 @@
       <c r="N17" s="6">
         <v>14</v>
       </c>
-      <c r="O17" s="29">
+      <c r="O17" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="Q17" s="6">
         <v>3</v>
       </c>
       <c r="R17" s="6">
         <f t="shared" si="3"/>
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="S17" s="14">
         <f t="shared" si="2"/>
@@ -3572,25 +3603,25 @@
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="18" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="23">
         <v>5</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="19">
         <v>1</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="23" t="s">
         <v>56</v>
       </c>
       <c r="L18" s="4" t="s">
@@ -3599,20 +3630,20 @@
       <c r="N18" s="6">
         <v>15</v>
       </c>
-      <c r="O18" s="29">
+      <c r="O18" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="1"/>
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="Q18" s="6">
         <v>8</v>
       </c>
       <c r="R18" s="6">
         <f t="shared" si="3"/>
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="S18" s="14">
         <f t="shared" si="2"/>
@@ -3620,25 +3651,25 @@
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="23">
-        <v>3</v>
-      </c>
-      <c r="J19" s="22">
+      <c r="I19" s="22">
+        <v>3</v>
+      </c>
+      <c r="J19" s="21">
         <v>2</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L19" s="4" t="s">
@@ -3647,20 +3678,20 @@
       <c r="N19" s="6">
         <v>16</v>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="1"/>
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
       </c>
       <c r="R19" s="6">
         <f t="shared" si="3"/>
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="S19" s="14">
         <f t="shared" si="2"/>
@@ -3668,25 +3699,25 @@
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="23">
-        <v>3</v>
-      </c>
-      <c r="J20" s="22">
+      <c r="I20" s="22">
+        <v>3</v>
+      </c>
+      <c r="J20" s="21">
         <v>2</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L20" s="4" t="s">
@@ -3695,20 +3726,20 @@
       <c r="N20" s="6">
         <v>17</v>
       </c>
-      <c r="O20" s="29">
+      <c r="O20" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="1"/>
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="Q20" s="6">
         <v>9</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="3"/>
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="S20" s="14">
         <f t="shared" si="2"/>
@@ -3716,25 +3747,25 @@
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="18" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <v>8</v>
       </c>
-      <c r="J21" s="21">
-        <v>3</v>
-      </c>
-      <c r="K21" s="20" t="s">
+      <c r="J21" s="20">
+        <v>3</v>
+      </c>
+      <c r="K21" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L21" s="4" t="s">
@@ -3743,20 +3774,20 @@
       <c r="N21" s="6">
         <v>18</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="1"/>
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="Q21" s="6">
         <v>4</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="3"/>
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="S21" s="14">
         <f t="shared" si="2"/>
@@ -3764,25 +3795,25 @@
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="26">
         <v>13</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="19">
         <v>1</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L22" s="4" t="s">
@@ -3791,20 +3822,20 @@
       <c r="N22" s="6">
         <v>19</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" si="1"/>
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="Q22" s="6">
         <v>10</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="S22" s="14">
         <f t="shared" si="2"/>
@@ -3812,25 +3843,25 @@
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H23" s="27" t="s">
+      <c r="H23" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="26">
         <v>13</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="19">
         <v>1</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L23" s="4" t="s">
@@ -3839,20 +3870,20 @@
       <c r="N23" s="6">
         <v>20</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="1"/>
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="3"/>
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="S23" s="14">
         <f t="shared" si="2"/>
@@ -3860,25 +3891,25 @@
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="25" t="s">
+      <c r="H24" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="24">
         <v>8</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="21">
         <v>2</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L24" s="4" t="s">
@@ -3887,20 +3918,20 @@
       <c r="N24" s="6">
         <v>21</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P24" s="6">
         <f t="shared" si="1"/>
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="Q24" s="6">
         <v>8</v>
       </c>
       <c r="R24" s="6">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="S24" s="14">
         <f t="shared" si="2"/>
@@ -3908,25 +3939,25 @@
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F25" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G25" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="H25" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="24">
         <v>8</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="21">
         <v>2</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L25" s="4" t="s">
@@ -3935,20 +3966,20 @@
       <c r="N25" s="6">
         <v>22</v>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="1"/>
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="Q25" s="6">
         <v>6</v>
       </c>
       <c r="R25" s="6">
         <f t="shared" si="3"/>
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="S25" s="14">
         <f t="shared" si="2"/>
@@ -3956,25 +3987,25 @@
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I26" s="23">
-        <v>3</v>
-      </c>
-      <c r="J26" s="21">
-        <v>3</v>
-      </c>
-      <c r="K26" s="20" t="s">
+      <c r="I26" s="22">
+        <v>3</v>
+      </c>
+      <c r="J26" s="20">
+        <v>3</v>
+      </c>
+      <c r="K26" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L26" s="4" t="s">
@@ -3983,20 +4014,20 @@
       <c r="N26" s="6">
         <v>23</v>
       </c>
-      <c r="O26" s="29">
+      <c r="O26" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="1"/>
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="Q26" s="6">
         <v>9</v>
       </c>
       <c r="R26" s="6">
         <f t="shared" si="3"/>
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="S26" s="14">
         <f t="shared" si="2"/>
@@ -4004,25 +4035,25 @@
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="18" t="s">
         <v>32</v>
       </c>
       <c r="F27" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="23">
         <v>5</v>
       </c>
-      <c r="J27" s="21">
-        <v>3</v>
-      </c>
-      <c r="K27" s="20" t="s">
+      <c r="J27" s="20">
+        <v>3</v>
+      </c>
+      <c r="K27" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L27" s="4" t="s">
@@ -4031,20 +4062,20 @@
       <c r="N27" s="6">
         <v>24</v>
       </c>
-      <c r="O27" s="29">
+      <c r="O27" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
       </c>
       <c r="R27" s="6">
         <f t="shared" si="3"/>
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="S27" s="14">
         <f t="shared" si="2"/>
@@ -4052,25 +4083,25 @@
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="24">
         <v>8</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="19">
         <v>1</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L28" s="4" t="s">
@@ -4079,20 +4110,20 @@
       <c r="N28" s="6">
         <v>25</v>
       </c>
-      <c r="O28" s="29">
+      <c r="O28" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P28" s="6">
         <f t="shared" si="1"/>
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="Q28" s="6">
         <v>7</v>
       </c>
       <c r="R28" s="6">
         <f t="shared" si="3"/>
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="S28" s="14">
         <f t="shared" si="2"/>
@@ -4100,25 +4131,25 @@
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="24">
         <v>8</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29" s="21">
         <v>2</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L29" s="4" t="s">
@@ -4127,20 +4158,20 @@
       <c r="N29" s="6">
         <v>26</v>
       </c>
-      <c r="O29" s="29">
+      <c r="O29" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P29" s="6">
         <f t="shared" si="1"/>
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="Q29" s="6">
         <v>5</v>
       </c>
       <c r="R29" s="6">
         <f t="shared" si="3"/>
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="S29" s="14">
         <f t="shared" si="2"/>
@@ -4148,25 +4179,25 @@
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
         <v>35</v>
       </c>
       <c r="F30" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G30" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="24" t="s">
+      <c r="H30" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="23">
         <v>5</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <v>1</v>
       </c>
-      <c r="K30" s="20" t="s">
+      <c r="K30" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L30" s="4" t="s">
@@ -4175,20 +4206,20 @@
       <c r="N30" s="6">
         <v>27</v>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P30" s="6">
         <f t="shared" si="1"/>
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="Q30" s="6">
         <v>6</v>
       </c>
       <c r="R30" s="6">
         <f t="shared" si="3"/>
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="S30" s="14">
         <f t="shared" si="2"/>
@@ -4196,25 +4227,25 @@
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F31" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="G31" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="24" t="s">
+      <c r="H31" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="23">
         <v>5</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="19">
         <v>1</v>
       </c>
-      <c r="K31" s="20" t="s">
+      <c r="K31" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L31" s="4" t="s">
@@ -4223,20 +4254,20 @@
       <c r="N31" s="6">
         <v>28</v>
       </c>
-      <c r="O31" s="29">
+      <c r="O31" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P31" s="6">
         <f t="shared" si="1"/>
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
       </c>
       <c r="R31" s="6">
         <f t="shared" si="3"/>
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="S31" s="14">
         <f t="shared" si="2"/>
@@ -4244,25 +4275,25 @@
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>37</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="23">
         <v>5</v>
       </c>
-      <c r="J32" s="21">
-        <v>3</v>
-      </c>
-      <c r="K32" s="20" t="s">
+      <c r="J32" s="20">
+        <v>3</v>
+      </c>
+      <c r="K32" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L32" s="4" t="s">
@@ -4271,20 +4302,20 @@
       <c r="N32" s="6">
         <v>29</v>
       </c>
-      <c r="O32" s="29">
+      <c r="O32" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P32" s="6">
         <f t="shared" si="1"/>
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="Q32" s="6">
         <v>4</v>
       </c>
       <c r="R32" s="6">
         <f t="shared" si="3"/>
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="S32" s="14">
         <f t="shared" si="2"/>
@@ -4292,25 +4323,25 @@
       </c>
     </row>
     <row r="33" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F33" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="23">
-        <v>3</v>
-      </c>
-      <c r="J33" s="21">
-        <v>3</v>
-      </c>
-      <c r="K33" s="20" t="s">
+      <c r="I33" s="22">
+        <v>3</v>
+      </c>
+      <c r="J33" s="20">
+        <v>3</v>
+      </c>
+      <c r="K33" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L33" s="4" t="s">
@@ -4319,20 +4350,20 @@
       <c r="N33" s="6">
         <v>30</v>
       </c>
-      <c r="O33" s="29">
+      <c r="O33" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P33" s="6">
         <f t="shared" si="1"/>
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="Q33" s="6">
         <v>3</v>
       </c>
       <c r="R33" s="6">
         <f t="shared" si="3"/>
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="S33" s="14">
         <f t="shared" si="2"/>
@@ -4340,25 +4371,25 @@
       </c>
     </row>
     <row r="34" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="I34" s="23">
-        <v>3</v>
-      </c>
-      <c r="J34" s="20">
+      <c r="I34" s="22">
+        <v>3</v>
+      </c>
+      <c r="J34" s="19">
         <v>1</v>
       </c>
-      <c r="K34" s="20" t="s">
+      <c r="K34" s="19" t="s">
         <v>88</v>
       </c>
       <c r="L34" s="4" t="s">
@@ -4367,20 +4398,20 @@
       <c r="N34" s="6">
         <v>31</v>
       </c>
-      <c r="O34" s="29">
+      <c r="O34" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P34" s="6">
         <f t="shared" si="1"/>
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="Q34" s="6">
         <v>1</v>
       </c>
       <c r="R34" s="6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="S34" s="14">
         <f t="shared" si="2"/>
@@ -4388,45 +4419,45 @@
       </c>
     </row>
     <row r="35" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="18" t="s">
         <v>90</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H35" s="27" t="s">
+      <c r="H35" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="26">
         <v>13</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="21">
         <v>2</v>
       </c>
-      <c r="K35" s="28" t="s">
+      <c r="K35" s="27" t="s">
         <v>100</v>
       </c>
       <c r="L35" s="4"/>
       <c r="N35" s="6">
         <v>32</v>
       </c>
-      <c r="O35" s="29">
+      <c r="O35" s="28">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P35" s="6">
         <f t="shared" si="1"/>
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
       </c>
       <c r="R35" s="6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="S35" s="14">
         <f t="shared" si="2"/>
@@ -4434,45 +4465,45 @@
       </c>
     </row>
     <row r="36" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="18" t="s">
         <v>91</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G36" s="21" t="s">
+      <c r="G36" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H36" s="26" t="s">
+      <c r="H36" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="25">
         <v>21</v>
       </c>
-      <c r="J36" s="21">
-        <v>3</v>
-      </c>
-      <c r="K36" s="28" t="s">
+      <c r="J36" s="20">
+        <v>3</v>
+      </c>
+      <c r="K36" s="27" t="s">
         <v>100</v>
       </c>
       <c r="L36" s="4"/>
       <c r="N36" s="6">
         <v>33</v>
       </c>
-      <c r="O36" s="29">
+      <c r="O36" s="28">
         <f t="shared" ref="O36:O67" si="4">$B$10</f>
         <v>3</v>
       </c>
       <c r="P36" s="6">
         <f t="shared" si="1"/>
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
       </c>
       <c r="R36" s="6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="S36" s="14">
         <f t="shared" si="2"/>
@@ -4480,45 +4511,45 @@
       </c>
     </row>
     <row r="37" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="18" t="s">
         <v>92</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G37" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="24">
         <v>8</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37" s="21">
         <v>2</v>
       </c>
-      <c r="K37" s="28" t="s">
+      <c r="K37" s="27" t="s">
         <v>100</v>
       </c>
       <c r="L37" s="4"/>
       <c r="N37" s="6">
         <v>34</v>
       </c>
-      <c r="O37" s="29">
+      <c r="O37" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P37" s="6">
         <f t="shared" si="1"/>
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="Q37" s="6">
         <v>0</v>
       </c>
       <c r="R37" s="6">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="S37" s="14">
         <f t="shared" si="2"/>
@@ -4526,45 +4557,45 @@
       </c>
     </row>
     <row r="38" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="18" t="s">
         <v>93</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H38" s="25" t="s">
+      <c r="H38" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="24">
         <v>8</v>
       </c>
-      <c r="J38" s="20">
+      <c r="J38" s="19">
         <v>1</v>
       </c>
-      <c r="K38" s="28" t="s">
+      <c r="K38" s="27" t="s">
         <v>100</v>
       </c>
       <c r="L38" s="4"/>
       <c r="N38" s="6">
         <v>35</v>
       </c>
-      <c r="O38" s="29">
+      <c r="O38" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P38" s="6">
         <f t="shared" si="1"/>
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="Q38" s="6">
         <v>8</v>
       </c>
       <c r="R38" s="6">
         <f t="shared" si="3"/>
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="S38" s="15">
         <f t="shared" si="2"/>
@@ -4572,45 +4603,45 @@
       </c>
     </row>
     <row r="39" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="31" t="s">
+      <c r="E39" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G39" s="34" t="s">
+      <c r="G39" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H39" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="34">
         <v>8</v>
       </c>
-      <c r="J39" s="36">
+      <c r="J39" s="35">
         <v>2</v>
       </c>
-      <c r="K39" s="37" t="s">
+      <c r="K39" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="L39" s="38"/>
+      <c r="L39" s="37"/>
       <c r="N39" s="6">
         <v>36</v>
       </c>
-      <c r="O39" s="29">
+      <c r="O39" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P39" s="6">
         <f t="shared" si="1"/>
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="Q39" s="6">
         <v>0</v>
       </c>
       <c r="R39" s="6">
         <f t="shared" si="3"/>
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="S39" s="15">
         <f t="shared" si="2"/>
@@ -4618,19 +4649,19 @@
       </c>
     </row>
     <row r="40" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="G40" s="40" t="s">
+      <c r="G40" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="H40" s="41" t="s">
+      <c r="H40" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="I40" s="41">
+      <c r="I40" s="40">
         <v>21</v>
       </c>
       <c r="J40" s="12">
@@ -4639,24 +4670,24 @@
       <c r="K40" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="39"/>
+      <c r="L40" s="38"/>
       <c r="N40" s="6">
         <v>37</v>
       </c>
-      <c r="O40" s="29">
+      <c r="O40" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P40" s="6">
         <f t="shared" si="1"/>
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="Q40" s="6">
         <v>6</v>
       </c>
       <c r="R40" s="6">
         <f t="shared" si="3"/>
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="S40" s="15">
         <f t="shared" si="2"/>
@@ -4664,45 +4695,45 @@
       </c>
     </row>
     <row r="41" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="F41" s="39" t="s">
+      <c r="F41" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="H41" s="42" t="s">
+      <c r="H41" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="I41" s="42">
+      <c r="I41" s="41">
         <v>13</v>
       </c>
-      <c r="J41" s="43">
+      <c r="J41" s="42">
         <v>2</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L41" s="39"/>
+      <c r="L41" s="38"/>
       <c r="N41" s="6">
         <v>38</v>
       </c>
-      <c r="O41" s="29">
+      <c r="O41" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P41" s="6">
         <f t="shared" si="1"/>
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="Q41" s="6">
         <v>0</v>
       </c>
       <c r="R41" s="6">
         <f t="shared" si="3"/>
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="S41" s="15">
         <f t="shared" si="2"/>
@@ -4713,20 +4744,20 @@
       <c r="N42" s="6">
         <v>39</v>
       </c>
-      <c r="O42" s="29">
+      <c r="O42" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P42" s="6">
         <f t="shared" si="1"/>
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="Q42" s="6">
         <v>8</v>
       </c>
       <c r="R42" s="6">
         <f t="shared" si="3"/>
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="S42" s="15">
         <f t="shared" si="2"/>
@@ -4737,20 +4768,20 @@
       <c r="N43" s="6">
         <v>40</v>
       </c>
-      <c r="O43" s="29">
+      <c r="O43" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="1"/>
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="Q43" s="6">
         <v>8</v>
       </c>
       <c r="R43" s="6">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="S43" s="15">
         <f t="shared" si="2"/>
@@ -4761,20 +4792,20 @@
       <c r="N44" s="6">
         <v>41</v>
       </c>
-      <c r="O44" s="29">
+      <c r="O44" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P44" s="6">
         <f t="shared" si="1"/>
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="Q44" s="6">
         <v>0</v>
       </c>
       <c r="R44" s="6">
         <f t="shared" si="3"/>
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="S44" s="15">
         <f t="shared" si="2"/>
@@ -4785,20 +4816,20 @@
       <c r="N45" s="6">
         <v>42</v>
       </c>
-      <c r="O45" s="29">
+      <c r="O45" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P45" s="6">
         <f t="shared" si="1"/>
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="Q45" s="6">
         <v>8</v>
       </c>
       <c r="R45" s="6">
         <f t="shared" si="3"/>
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="S45" s="15">
         <f t="shared" si="2"/>
@@ -4809,20 +4840,20 @@
       <c r="N46" s="6">
         <v>43</v>
       </c>
-      <c r="O46" s="29">
+      <c r="O46" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P46" s="6">
         <f t="shared" si="1"/>
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="Q46" s="6">
         <v>10</v>
       </c>
       <c r="R46" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S46" s="15">
         <f t="shared" si="2"/>
@@ -4833,20 +4864,20 @@
       <c r="N47" s="6">
         <v>44</v>
       </c>
-      <c r="O47" s="29">
+      <c r="O47" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P47" s="6">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="6">
         <v>0</v>
       </c>
       <c r="R47" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S47" s="15">
         <f t="shared" si="2"/>
@@ -4857,20 +4888,20 @@
       <c r="N48" s="6">
         <v>45</v>
       </c>
-      <c r="O48" s="29">
+      <c r="O48" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P48" s="6">
         <f t="shared" si="1"/>
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="6">
         <v>0</v>
       </c>
       <c r="R48" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S48" s="15">
         <f t="shared" si="2"/>
@@ -4881,20 +4912,20 @@
       <c r="N49" s="6">
         <v>46</v>
       </c>
-      <c r="O49" s="29">
+      <c r="O49" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P49" s="6">
         <f t="shared" si="1"/>
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="6">
         <v>0</v>
       </c>
       <c r="R49" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S49" s="15">
         <f t="shared" si="2"/>
@@ -4905,20 +4936,20 @@
       <c r="N50" s="6">
         <v>47</v>
       </c>
-      <c r="O50" s="29">
+      <c r="O50" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P50" s="6">
         <f t="shared" si="1"/>
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="Q50" s="6">
         <v>0</v>
       </c>
       <c r="R50" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S50" s="15">
         <f t="shared" si="2"/>
@@ -4929,20 +4960,20 @@
       <c r="N51" s="6">
         <v>48</v>
       </c>
-      <c r="O51" s="29">
+      <c r="O51" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P51" s="6">
         <f t="shared" si="1"/>
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="Q51" s="6">
         <v>0</v>
       </c>
       <c r="R51" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S51" s="15">
         <f t="shared" si="2"/>
@@ -4953,20 +4984,20 @@
       <c r="N52" s="6">
         <v>49</v>
       </c>
-      <c r="O52" s="29">
+      <c r="O52" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P52" s="6">
         <f t="shared" si="1"/>
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="Q52" s="6">
         <v>0</v>
       </c>
       <c r="R52" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S52" s="15">
         <f t="shared" si="2"/>
@@ -4977,20 +5008,20 @@
       <c r="N53" s="6">
         <v>50</v>
       </c>
-      <c r="O53" s="29">
+      <c r="O53" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P53" s="6">
         <f t="shared" si="1"/>
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="Q53" s="6">
         <v>0</v>
       </c>
       <c r="R53" s="6">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="S53" s="15">
         <f t="shared" si="2"/>
@@ -5001,20 +5032,20 @@
       <c r="N54" s="6">
         <v>51</v>
       </c>
-      <c r="O54" s="29">
+      <c r="O54" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P54" s="6">
         <f t="shared" si="1"/>
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="Q54" s="6">
         <v>8</v>
       </c>
       <c r="R54" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="S54" s="15">
         <f t="shared" si="2"/>
@@ -5025,20 +5056,20 @@
       <c r="N55" s="6">
         <v>52</v>
       </c>
-      <c r="O55" s="29">
+      <c r="O55" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P55" s="6">
         <f t="shared" si="1"/>
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="Q55" s="6">
         <v>0</v>
       </c>
       <c r="R55" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="S55" s="15">
         <f t="shared" si="2"/>
@@ -5049,20 +5080,20 @@
       <c r="N56" s="6">
         <v>53</v>
       </c>
-      <c r="O56" s="29">
+      <c r="O56" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P56" s="6">
         <f t="shared" si="1"/>
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="Q56" s="6">
         <v>0</v>
       </c>
       <c r="R56" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="S56" s="15">
         <f t="shared" si="2"/>
@@ -5073,20 +5104,20 @@
       <c r="N57" s="6">
         <v>54</v>
       </c>
-      <c r="O57" s="29">
+      <c r="O57" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P57" s="6">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="Q57" s="6">
         <v>0</v>
       </c>
       <c r="R57" s="6">
         <f t="shared" si="3"/>
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="S57" s="15">
         <f t="shared" si="2"/>
@@ -5097,20 +5128,20 @@
       <c r="N58" s="6">
         <v>55</v>
       </c>
-      <c r="O58" s="29">
+      <c r="O58" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P58" s="6">
         <f t="shared" si="1"/>
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="Q58" s="6">
         <v>13</v>
       </c>
       <c r="R58" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="S58" s="15">
         <f t="shared" si="2"/>
@@ -5121,20 +5152,20 @@
       <c r="N59" s="6">
         <v>56</v>
       </c>
-      <c r="O59" s="29">
+      <c r="O59" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P59" s="6">
         <f t="shared" si="1"/>
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="Q59" s="6">
         <v>0</v>
       </c>
       <c r="R59" s="6">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="S59" s="15">
         <f t="shared" si="2"/>
@@ -5145,20 +5176,20 @@
       <c r="N60" s="6">
         <v>57</v>
       </c>
-      <c r="O60" s="29">
+      <c r="O60" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P60" s="6">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="Q60" s="6">
         <v>3</v>
       </c>
       <c r="R60" s="6">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="S60" s="15">
         <f t="shared" si="2"/>
@@ -5169,20 +5200,20 @@
       <c r="N61" s="6">
         <v>58</v>
       </c>
-      <c r="O61" s="29">
+      <c r="O61" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P61" s="6">
         <f t="shared" si="1"/>
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="Q61" s="6">
         <v>0</v>
       </c>
       <c r="R61" s="6">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="S61" s="15">
         <f t="shared" si="2"/>
@@ -5193,20 +5224,20 @@
       <c r="N62" s="6">
         <v>59</v>
       </c>
-      <c r="O62" s="29">
+      <c r="O62" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P62" s="6">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="Q62" s="6">
         <v>0</v>
       </c>
       <c r="R62" s="6">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="S62" s="15">
         <f t="shared" si="2"/>
@@ -5217,20 +5248,20 @@
       <c r="N63" s="6">
         <v>60</v>
       </c>
-      <c r="O63" s="29">
+      <c r="O63" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P63" s="6">
         <f t="shared" si="1"/>
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="Q63" s="6">
         <v>0</v>
       </c>
       <c r="R63" s="6">
         <f t="shared" si="3"/>
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="S63" s="15">
         <f t="shared" si="2"/>
@@ -5241,20 +5272,20 @@
       <c r="N64" s="6">
         <v>61</v>
       </c>
-      <c r="O64" s="29">
+      <c r="O64" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P64" s="6">
         <f t="shared" si="1"/>
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="Q64" s="6">
         <v>8</v>
       </c>
       <c r="R64" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S64" s="15">
         <f t="shared" si="2"/>
@@ -5265,20 +5296,20 @@
       <c r="N65" s="6">
         <v>62</v>
       </c>
-      <c r="O65" s="29">
+      <c r="O65" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P65" s="6">
         <f t="shared" si="1"/>
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="Q65" s="6">
         <v>0</v>
       </c>
       <c r="R65" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S65" s="15">
         <f t="shared" si="2"/>
@@ -5289,20 +5320,20 @@
       <c r="N66" s="6">
         <v>63</v>
       </c>
-      <c r="O66" s="29">
+      <c r="O66" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P66" s="6">
         <f t="shared" si="1"/>
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="Q66" s="6">
         <v>0</v>
       </c>
       <c r="R66" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S66" s="15">
         <f t="shared" si="2"/>
@@ -5313,20 +5344,20 @@
       <c r="N67" s="6">
         <v>64</v>
       </c>
-      <c r="O67" s="29">
+      <c r="O67" s="28">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="P67" s="6">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Q67" s="6">
         <v>0</v>
       </c>
       <c r="R67" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S67" s="15">
         <f t="shared" si="2"/>
@@ -5337,20 +5368,20 @@
       <c r="N68" s="6">
         <v>65</v>
       </c>
-      <c r="O68" s="29">
+      <c r="O68" s="28">
         <f t="shared" ref="O68:O99" si="5">$B$10</f>
         <v>3</v>
       </c>
       <c r="P68" s="6">
         <f t="shared" si="1"/>
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="Q68" s="6">
         <v>0</v>
       </c>
       <c r="R68" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S68" s="15">
         <f t="shared" si="2"/>
@@ -5361,20 +5392,20 @@
       <c r="N69" s="6">
         <v>66</v>
       </c>
-      <c r="O69" s="29">
+      <c r="O69" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P69" s="6">
         <f t="shared" ref="P69:P93" si="6">P68-$O$4</f>
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="Q69" s="6">
         <v>0</v>
       </c>
       <c r="R69" s="6">
         <f t="shared" si="3"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S69" s="15">
         <f t="shared" ref="S69:S117" si="7">S68+1</f>
@@ -5385,20 +5416,20 @@
       <c r="N70" s="6">
         <v>67</v>
       </c>
-      <c r="O70" s="29">
+      <c r="O70" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P70" s="6">
         <f t="shared" si="6"/>
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="Q70" s="6">
         <v>0</v>
       </c>
       <c r="R70" s="6">
         <f t="shared" ref="R70:R117" si="8">IF(Q70&lt;&gt;"",R69-Q70,R69)</f>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S70" s="15">
         <f t="shared" si="7"/>
@@ -5409,20 +5440,20 @@
       <c r="N71" s="6">
         <v>68</v>
       </c>
-      <c r="O71" s="29">
+      <c r="O71" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P71" s="6">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="Q71" s="6">
         <v>0</v>
       </c>
       <c r="R71" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S71" s="15">
         <f t="shared" si="7"/>
@@ -5433,20 +5464,20 @@
       <c r="N72" s="6">
         <v>69</v>
       </c>
-      <c r="O72" s="29">
+      <c r="O72" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P72" s="6">
         <f t="shared" si="6"/>
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="Q72" s="6">
         <v>0</v>
       </c>
       <c r="R72" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S72" s="15">
         <f t="shared" si="7"/>
@@ -5457,20 +5488,20 @@
       <c r="N73" s="6">
         <v>70</v>
       </c>
-      <c r="O73" s="29">
+      <c r="O73" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P73" s="6">
         <f t="shared" si="6"/>
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="Q73" s="6">
         <v>0</v>
       </c>
       <c r="R73" s="6">
         <f t="shared" si="8"/>
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="S73" s="15">
         <f t="shared" si="7"/>
@@ -5481,20 +5512,20 @@
       <c r="N74" s="6">
         <v>71</v>
       </c>
-      <c r="O74" s="29">
+      <c r="O74" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P74" s="6">
         <f t="shared" si="6"/>
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="Q74" s="6">
         <v>3</v>
       </c>
       <c r="R74" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="S74" s="15">
         <f t="shared" si="7"/>
@@ -5505,20 +5536,20 @@
       <c r="N75" s="6">
         <v>72</v>
       </c>
-      <c r="O75" s="29">
+      <c r="O75" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P75" s="6">
         <f t="shared" si="6"/>
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="Q75" s="6">
         <v>0</v>
       </c>
       <c r="R75" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="S75" s="15">
         <f t="shared" si="7"/>
@@ -5529,18 +5560,20 @@
       <c r="N76" s="6">
         <v>73</v>
       </c>
-      <c r="O76" s="29">
+      <c r="O76" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P76" s="6">
         <f t="shared" si="6"/>
-        <v>53</v>
-      </c>
-      <c r="Q76" s="6"/>
+        <v>87</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>13</v>
+      </c>
       <c r="R76" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S76" s="15">
         <f t="shared" si="7"/>
@@ -5551,18 +5584,20 @@
       <c r="N77" s="6">
         <v>74</v>
       </c>
-      <c r="O77" s="29">
+      <c r="O77" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P77" s="6">
         <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="Q77" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0</v>
+      </c>
       <c r="R77" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S77" s="15">
         <f t="shared" si="7"/>
@@ -5573,18 +5608,20 @@
       <c r="N78" s="6">
         <v>75</v>
       </c>
-      <c r="O78" s="29">
+      <c r="O78" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P78" s="6">
         <f t="shared" si="6"/>
-        <v>47</v>
-      </c>
-      <c r="Q78" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>0</v>
+      </c>
       <c r="R78" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S78" s="15">
         <f t="shared" si="7"/>
@@ -5595,18 +5632,20 @@
       <c r="N79" s="6">
         <v>76</v>
       </c>
-      <c r="O79" s="29">
+      <c r="O79" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P79" s="6">
         <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-      <c r="Q79" s="6"/>
+        <v>78</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>0</v>
+      </c>
       <c r="R79" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S79" s="15">
         <f t="shared" si="7"/>
@@ -5617,18 +5656,20 @@
       <c r="N80" s="6">
         <v>77</v>
       </c>
-      <c r="O80" s="29">
+      <c r="O80" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-      <c r="Q80" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>0</v>
+      </c>
       <c r="R80" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S80" s="15">
         <f t="shared" si="7"/>
@@ -5639,18 +5680,20 @@
       <c r="N81" s="6">
         <v>78</v>
       </c>
-      <c r="O81" s="29">
+      <c r="O81" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P81" s="6">
         <f t="shared" si="6"/>
-        <v>38</v>
-      </c>
-      <c r="Q81" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>0</v>
+      </c>
       <c r="R81" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S81" s="15">
         <f t="shared" si="7"/>
@@ -5661,18 +5704,20 @@
       <c r="N82" s="6">
         <v>79</v>
       </c>
-      <c r="O82" s="29">
+      <c r="O82" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P82" s="6">
         <f t="shared" si="6"/>
-        <v>35</v>
-      </c>
-      <c r="Q82" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>0</v>
+      </c>
       <c r="R82" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S82" s="15">
         <f t="shared" si="7"/>
@@ -5683,18 +5728,20 @@
       <c r="N83" s="6">
         <v>80</v>
       </c>
-      <c r="O83" s="29">
+      <c r="O83" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P83" s="6">
         <f t="shared" si="6"/>
-        <v>32</v>
-      </c>
-      <c r="Q83" s="6"/>
+        <v>66</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>0</v>
+      </c>
       <c r="R83" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S83" s="15">
         <f t="shared" si="7"/>
@@ -5705,18 +5752,20 @@
       <c r="N84" s="6">
         <v>81</v>
       </c>
-      <c r="O84" s="29">
+      <c r="O84" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P84" s="6">
         <f t="shared" si="6"/>
-        <v>29</v>
-      </c>
-      <c r="Q84" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>0</v>
+      </c>
       <c r="R84" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S84" s="15">
         <f t="shared" si="7"/>
@@ -5727,18 +5776,20 @@
       <c r="N85" s="6">
         <v>82</v>
       </c>
-      <c r="O85" s="29">
+      <c r="O85" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P85" s="6">
         <f t="shared" si="6"/>
-        <v>26</v>
-      </c>
-      <c r="Q85" s="6"/>
+        <v>60</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>0</v>
+      </c>
       <c r="R85" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S85" s="15">
         <f t="shared" si="7"/>
@@ -5749,18 +5800,20 @@
       <c r="N86" s="6">
         <v>83</v>
       </c>
-      <c r="O86" s="29">
+      <c r="O86" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P86" s="6">
         <f t="shared" si="6"/>
-        <v>23</v>
-      </c>
-      <c r="Q86" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>0</v>
+      </c>
       <c r="R86" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S86" s="15">
         <f t="shared" si="7"/>
@@ -5771,18 +5824,20 @@
       <c r="N87" s="6">
         <v>84</v>
       </c>
-      <c r="O87" s="29">
+      <c r="O87" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P87" s="6">
         <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="Q87" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>0</v>
+      </c>
       <c r="R87" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S87" s="15">
         <f t="shared" si="7"/>
@@ -5793,18 +5848,18 @@
       <c r="N88" s="6">
         <v>85</v>
       </c>
-      <c r="O88" s="29">
+      <c r="O88" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P88" s="6">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S88" s="16">
         <f t="shared" si="7"/>
@@ -5815,18 +5870,18 @@
       <c r="N89" s="6">
         <v>86</v>
       </c>
-      <c r="O89" s="29">
+      <c r="O89" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P89" s="6">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="Q89" s="6"/>
       <c r="R89" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S89" s="16">
         <f t="shared" si="7"/>
@@ -5837,18 +5892,18 @@
       <c r="N90" s="6">
         <v>87</v>
       </c>
-      <c r="O90" s="29">
+      <c r="O90" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P90" s="6">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S90" s="16">
         <f t="shared" si="7"/>
@@ -5859,18 +5914,18 @@
       <c r="N91" s="6">
         <v>88</v>
       </c>
-      <c r="O91" s="29">
+      <c r="O91" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P91" s="6">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="Q91" s="6"/>
       <c r="R91" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S91" s="16">
         <f t="shared" si="7"/>
@@ -5881,18 +5936,18 @@
       <c r="N92" s="6">
         <v>89</v>
       </c>
-      <c r="O92" s="29">
+      <c r="O92" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P92" s="6">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S92" s="16">
         <f t="shared" si="7"/>
@@ -5903,18 +5958,18 @@
       <c r="N93" s="6">
         <v>90</v>
       </c>
-      <c r="O93" s="29">
+      <c r="O93" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="P93" s="6">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="Q93" s="6"/>
       <c r="R93" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S93" s="16">
         <f t="shared" si="7"/>
@@ -5925,7 +5980,7 @@
       <c r="N94" s="6">
         <v>91</v>
       </c>
-      <c r="O94" s="29">
+      <c r="O94" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -5935,7 +5990,7 @@
       <c r="Q94" s="6"/>
       <c r="R94" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S94" s="16">
         <f t="shared" si="7"/>
@@ -5946,7 +6001,7 @@
       <c r="N95" s="6">
         <v>92</v>
       </c>
-      <c r="O95" s="29">
+      <c r="O95" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -5956,7 +6011,7 @@
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S95" s="16">
         <f t="shared" si="7"/>
@@ -5967,7 +6022,7 @@
       <c r="N96" s="6">
         <v>93</v>
       </c>
-      <c r="O96" s="29">
+      <c r="O96" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -5977,7 +6032,7 @@
       <c r="Q96" s="6"/>
       <c r="R96" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S96" s="16">
         <f t="shared" si="7"/>
@@ -5988,7 +6043,7 @@
       <c r="N97" s="6">
         <v>94</v>
       </c>
-      <c r="O97" s="29">
+      <c r="O97" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -5998,7 +6053,7 @@
       <c r="Q97" s="6"/>
       <c r="R97" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S97" s="16">
         <f t="shared" si="7"/>
@@ -6009,7 +6064,7 @@
       <c r="N98" s="6">
         <v>95</v>
       </c>
-      <c r="O98" s="29">
+      <c r="O98" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -6019,7 +6074,7 @@
       <c r="Q98" s="6"/>
       <c r="R98" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S98" s="16">
         <f t="shared" si="7"/>
@@ -6030,7 +6085,7 @@
       <c r="N99" s="6">
         <v>96</v>
       </c>
-      <c r="O99" s="29">
+      <c r="O99" s="28">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -6040,7 +6095,7 @@
       <c r="Q99" s="6"/>
       <c r="R99" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S99" s="16">
         <f t="shared" si="7"/>
@@ -6051,7 +6106,7 @@
       <c r="N100" s="6">
         <v>97</v>
       </c>
-      <c r="O100" s="29">
+      <c r="O100" s="28">
         <f t="shared" ref="O100:O117" si="9">$B$10</f>
         <v>3</v>
       </c>
@@ -6061,7 +6116,7 @@
       <c r="Q100" s="6"/>
       <c r="R100" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S100" s="16">
         <f t="shared" si="7"/>
@@ -6072,7 +6127,7 @@
       <c r="N101" s="6">
         <v>98</v>
       </c>
-      <c r="O101" s="29">
+      <c r="O101" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6082,7 +6137,7 @@
       <c r="Q101" s="6"/>
       <c r="R101" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S101" s="16">
         <f t="shared" si="7"/>
@@ -6093,7 +6148,7 @@
       <c r="N102" s="6">
         <v>99</v>
       </c>
-      <c r="O102" s="29">
+      <c r="O102" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6103,7 +6158,7 @@
       <c r="Q102" s="6"/>
       <c r="R102" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S102" s="16">
         <f t="shared" si="7"/>
@@ -6114,7 +6169,7 @@
       <c r="N103" s="6">
         <v>100</v>
       </c>
-      <c r="O103" s="29">
+      <c r="O103" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6124,7 +6179,7 @@
       <c r="Q103" s="6"/>
       <c r="R103" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S103" s="16">
         <f t="shared" si="7"/>
@@ -6135,7 +6190,7 @@
       <c r="N104" s="6">
         <v>101</v>
       </c>
-      <c r="O104" s="29">
+      <c r="O104" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6145,7 +6200,7 @@
       <c r="Q104" s="6"/>
       <c r="R104" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S104" s="16">
         <f t="shared" si="7"/>
@@ -6156,7 +6211,7 @@
       <c r="N105" s="6">
         <v>102</v>
       </c>
-      <c r="O105" s="29">
+      <c r="O105" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6166,7 +6221,7 @@
       <c r="Q105" s="6"/>
       <c r="R105" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S105" s="16">
         <f t="shared" si="7"/>
@@ -6177,7 +6232,7 @@
       <c r="N106" s="6">
         <v>103</v>
       </c>
-      <c r="O106" s="29">
+      <c r="O106" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6187,7 +6242,7 @@
       <c r="Q106" s="6"/>
       <c r="R106" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S106" s="16">
         <f t="shared" si="7"/>
@@ -6198,7 +6253,7 @@
       <c r="N107" s="6">
         <v>104</v>
       </c>
-      <c r="O107" s="29">
+      <c r="O107" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6208,7 +6263,7 @@
       <c r="Q107" s="6"/>
       <c r="R107" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S107" s="16">
         <f t="shared" si="7"/>
@@ -6219,7 +6274,7 @@
       <c r="N108" s="6">
         <v>105</v>
       </c>
-      <c r="O108" s="29">
+      <c r="O108" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6229,7 +6284,7 @@
       <c r="Q108" s="6"/>
       <c r="R108" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S108" s="16">
         <f t="shared" si="7"/>
@@ -6240,7 +6295,7 @@
       <c r="N109" s="6">
         <v>106</v>
       </c>
-      <c r="O109" s="29">
+      <c r="O109" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6250,7 +6305,7 @@
       <c r="Q109" s="6"/>
       <c r="R109" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S109" s="16">
         <f t="shared" si="7"/>
@@ -6261,7 +6316,7 @@
       <c r="N110" s="6">
         <v>107</v>
       </c>
-      <c r="O110" s="29">
+      <c r="O110" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6271,7 +6326,7 @@
       <c r="Q110" s="6"/>
       <c r="R110" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S110" s="16">
         <f t="shared" si="7"/>
@@ -6282,7 +6337,7 @@
       <c r="N111" s="6">
         <v>108</v>
       </c>
-      <c r="O111" s="29">
+      <c r="O111" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6292,7 +6347,7 @@
       <c r="Q111" s="6"/>
       <c r="R111" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S111" s="16">
         <f t="shared" si="7"/>
@@ -6303,7 +6358,7 @@
       <c r="N112" s="6">
         <v>109</v>
       </c>
-      <c r="O112" s="29">
+      <c r="O112" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6313,7 +6368,7 @@
       <c r="Q112" s="6"/>
       <c r="R112" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S112" s="16">
         <f t="shared" si="7"/>
@@ -6324,7 +6379,7 @@
       <c r="N113" s="6">
         <v>110</v>
       </c>
-      <c r="O113" s="29">
+      <c r="O113" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6334,7 +6389,7 @@
       <c r="Q113" s="6"/>
       <c r="R113" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S113" s="16">
         <f t="shared" si="7"/>
@@ -6345,7 +6400,7 @@
       <c r="N114" s="6">
         <v>111</v>
       </c>
-      <c r="O114" s="29">
+      <c r="O114" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6355,7 +6410,7 @@
       <c r="Q114" s="6"/>
       <c r="R114" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S114" s="16">
         <f t="shared" si="7"/>
@@ -6366,7 +6421,7 @@
       <c r="N115" s="6">
         <v>112</v>
       </c>
-      <c r="O115" s="29">
+      <c r="O115" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6376,7 +6431,7 @@
       <c r="Q115" s="6"/>
       <c r="R115" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S115" s="16">
         <f t="shared" si="7"/>
@@ -6387,7 +6442,7 @@
       <c r="N116" s="6">
         <v>113</v>
       </c>
-      <c r="O116" s="29">
+      <c r="O116" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6397,7 +6452,7 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S116" s="16">
         <f t="shared" si="7"/>
@@ -6408,7 +6463,7 @@
       <c r="N117" s="6">
         <v>114</v>
       </c>
-      <c r="O117" s="29">
+      <c r="O117" s="28">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
@@ -6418,7 +6473,7 @@
       <c r="Q117" s="6"/>
       <c r="R117" s="6">
         <f t="shared" si="8"/>
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="S117" s="16">
         <f t="shared" si="7"/>
@@ -6488,4 +6543,1040 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75F2143-54FC-4EB9-9F76-FF403458FEED}">
+  <dimension ref="F6:Q22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="10" max="10" width="42.28515625" customWidth="1"/>
+    <col min="11" max="11" width="54.140625" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F7" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="22">
+        <v>3</v>
+      </c>
+      <c r="O7" s="20">
+        <v>3</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F8" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="4">
+        <v>8</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="24">
+        <v>8</v>
+      </c>
+      <c r="O8" s="19">
+        <v>1</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="4">
+        <v>13</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="26">
+        <v>13</v>
+      </c>
+      <c r="O9" s="19">
+        <v>1</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F10" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="4">
+        <v>21</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="26">
+        <v>13</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1</v>
+      </c>
+      <c r="P10" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J11" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="26">
+        <v>13</v>
+      </c>
+      <c r="O11" s="21">
+        <v>2</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(N7:N22)</f>
+        <v>113</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="24">
+        <v>8</v>
+      </c>
+      <c r="O12" s="19">
+        <v>1</v>
+      </c>
+      <c r="P12" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F13" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="6">
+        <v>114</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="23">
+        <v>5</v>
+      </c>
+      <c r="O13" s="21">
+        <v>2</v>
+      </c>
+      <c r="P13" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F14" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="6">
+        <f>ROUNDUP(G12/G13, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="22">
+        <v>3</v>
+      </c>
+      <c r="O14" s="20">
+        <v>3</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F15" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="26">
+        <v>13</v>
+      </c>
+      <c r="O15" s="19">
+        <v>1</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="24">
+        <v>8</v>
+      </c>
+      <c r="O16" s="19">
+        <v>1</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F17" s="5"/>
+      <c r="J17" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N17" s="23">
+        <v>5</v>
+      </c>
+      <c r="O17" s="21">
+        <v>2</v>
+      </c>
+      <c r="P17" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F18" s="5"/>
+      <c r="J18" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="23">
+        <v>5</v>
+      </c>
+      <c r="O18" s="21">
+        <v>2</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J19" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="22">
+        <v>3</v>
+      </c>
+      <c r="O19" s="20">
+        <v>3</v>
+      </c>
+      <c r="P19" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="23">
+        <v>5</v>
+      </c>
+      <c r="O20" s="20">
+        <v>3</v>
+      </c>
+      <c r="P20" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J21" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="22">
+        <v>3</v>
+      </c>
+      <c r="O21" s="19">
+        <v>1</v>
+      </c>
+      <c r="P21" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J22" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N22" s="23">
+        <v>5</v>
+      </c>
+      <c r="O22" s="19">
+        <v>1</v>
+      </c>
+      <c r="P22" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A6F73D-688A-4FEB-83F7-0ACA13147534}">
+  <dimension ref="F6:Q22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="10" max="10" width="41.42578125" customWidth="1"/>
+    <col min="11" max="11" width="45.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F6" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F7" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="22">
+        <v>3</v>
+      </c>
+      <c r="O7" s="21">
+        <v>2</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F8" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="4">
+        <v>8</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="22">
+        <v>3</v>
+      </c>
+      <c r="O8" s="21">
+        <v>2</v>
+      </c>
+      <c r="P8" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="4">
+        <v>13</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="24">
+        <v>8</v>
+      </c>
+      <c r="O9" s="20">
+        <v>3</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F10" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="4">
+        <v>21</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="26">
+        <v>13</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J11" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="26">
+        <v>13</v>
+      </c>
+      <c r="O11" s="19">
+        <v>1</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="6">
+        <f>SUM(N7:N22)</f>
+        <v>101</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" s="24">
+        <v>8</v>
+      </c>
+      <c r="O12" s="21">
+        <v>2</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F13" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="6">
+        <v>114</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N13" s="24">
+        <v>8</v>
+      </c>
+      <c r="O13" s="21">
+        <v>2</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F14" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="6">
+        <f>ROUNDUP(G12/G13, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="22">
+        <v>3</v>
+      </c>
+      <c r="O14" s="20">
+        <v>3</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F15" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15" s="23">
+        <v>5</v>
+      </c>
+      <c r="O15" s="20">
+        <v>3</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J16" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="24">
+        <v>8</v>
+      </c>
+      <c r="O16" s="19">
+        <v>1</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F17" s="5"/>
+      <c r="J17" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="N17" s="24">
+        <v>8</v>
+      </c>
+      <c r="O17" s="21">
+        <v>2</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="F18" s="5"/>
+      <c r="J18" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="23">
+        <v>5</v>
+      </c>
+      <c r="O18" s="19">
+        <v>1</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J19" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="23">
+        <v>5</v>
+      </c>
+      <c r="O19" s="19">
+        <v>1</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J20" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="23">
+        <v>5</v>
+      </c>
+      <c r="O20" s="20">
+        <v>3</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="22">
+        <v>3</v>
+      </c>
+      <c r="O21" s="20">
+        <v>3</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="6:17" x14ac:dyDescent="0.25">
+      <c r="J22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="22">
+        <v>3</v>
+      </c>
+      <c r="O22" s="19">
+        <v>1</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>